--- a/research/traditional_assets/database/data/croatia/croatia_construction_supplies.xlsx
+++ b/research/traditional_assets/database/data/croatia/croatia_construction_supplies.xlsx
@@ -1266,7 +1266,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1403,22 +1403,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.08823337625574057</v>
+        <v>0.08811145617848025</v>
       </c>
       <c r="C2">
-        <v>71.66022791739401</v>
+        <v>71.12066055948256</v>
       </c>
       <c r="D2">
-        <v>61.16022791739401</v>
+        <v>61.33646055948256</v>
       </c>
       <c r="E2">
-        <v>-1.08</v>
+        <v>-0.3642000000000001</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>0.7158</v>
       </c>
       <c r="G2">
         <v>10.5</v>
@@ -1439,28 +1439,28 @@
         <v>7.819999999999999</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.03600474</v>
       </c>
       <c r="N2">
-        <v>7.819999999999999</v>
+        <v>7.783995259999999</v>
       </c>
       <c r="O2">
-        <v>1.4076</v>
+        <v>1.4011191468</v>
       </c>
       <c r="P2">
-        <v>6.4124</v>
+        <v>6.3828761132</v>
       </c>
       <c r="Q2">
-        <v>13.1924</v>
+        <v>13.1628761132</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.08823337625574057</v>
+        <v>0.08858484462472752</v>
       </c>
       <c r="T2">
-        <v>0.7154876843770529</v>
+        <v>0.7214139460052265</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1477,7 +1477,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>217.1936250615891</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1485,22 +1485,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.08811145617848025</v>
+        <v>0.08798953610121991</v>
       </c>
       <c r="C3">
-        <v>71.12066055948256</v>
+        <v>70.58211176206385</v>
       </c>
       <c r="D3">
-        <v>61.33646055948256</v>
+        <v>61.51371176206384</v>
       </c>
       <c r="E3">
-        <v>-0.3642000000000001</v>
+        <v>0.3515999999999999</v>
       </c>
       <c r="F3">
-        <v>0.7158</v>
+        <v>1.4316</v>
       </c>
       <c r="G3">
         <v>10.5</v>
@@ -1521,28 +1521,28 @@
         <v>7.819999999999999</v>
       </c>
       <c r="M3">
-        <v>0.03600474</v>
+        <v>0.07200948</v>
       </c>
       <c r="N3">
-        <v>7.783995259999999</v>
+        <v>7.747990519999999</v>
       </c>
       <c r="O3">
-        <v>1.4011191468</v>
+        <v>1.3946382936</v>
       </c>
       <c r="P3">
-        <v>6.3828761132</v>
+        <v>6.353352226399999</v>
       </c>
       <c r="Q3">
-        <v>13.1628761132</v>
+        <v>13.1333522264</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.08858484462472752</v>
+        <v>0.08894348581757133</v>
       </c>
       <c r="T3">
-        <v>0.7214139460052265</v>
+        <v>0.7274611517482608</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1559,7 +1559,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>217.1936250615891</v>
+        <v>108.5968125307946</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1567,22 +1567,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.08798953610121991</v>
+        <v>0.08786761602395957</v>
       </c>
       <c r="C4">
-        <v>70.58211176206385</v>
+        <v>70.04459038109302</v>
       </c>
       <c r="D4">
-        <v>61.51371176206384</v>
+        <v>61.69199038109302</v>
       </c>
       <c r="E4">
-        <v>0.3515999999999999</v>
+        <v>1.0674</v>
       </c>
       <c r="F4">
-        <v>1.4316</v>
+        <v>2.1474</v>
       </c>
       <c r="G4">
         <v>10.5</v>
@@ -1603,28 +1603,28 @@
         <v>7.819999999999999</v>
       </c>
       <c r="M4">
-        <v>0.07200948</v>
+        <v>0.10801422</v>
       </c>
       <c r="N4">
-        <v>7.747990519999999</v>
+        <v>7.711985779999999</v>
       </c>
       <c r="O4">
-        <v>1.3946382936</v>
+        <v>1.3881574404</v>
       </c>
       <c r="P4">
-        <v>6.353352226399999</v>
+        <v>6.323828339599999</v>
       </c>
       <c r="Q4">
-        <v>13.1333522264</v>
+        <v>13.1038283396</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.08894348581757133</v>
+        <v>0.08930952167418513</v>
       </c>
       <c r="T4">
-        <v>0.7274611517482608</v>
+        <v>0.7336330421457906</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1641,7 +1641,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>108.5968125307946</v>
+        <v>72.39787502052971</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1649,22 +1649,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.08786761602395957</v>
+        <v>0.08774569594669922</v>
       </c>
       <c r="C5">
-        <v>70.04459038109302</v>
+        <v>69.50810537548875</v>
       </c>
       <c r="D5">
-        <v>61.69199038109302</v>
+        <v>61.87130537548876</v>
       </c>
       <c r="E5">
-        <v>1.0674</v>
+        <v>1.7832</v>
       </c>
       <c r="F5">
-        <v>2.1474</v>
+        <v>2.8632</v>
       </c>
       <c r="G5">
         <v>10.5</v>
@@ -1685,28 +1685,28 @@
         <v>7.819999999999999</v>
       </c>
       <c r="M5">
-        <v>0.10801422</v>
+        <v>0.14401896</v>
       </c>
       <c r="N5">
-        <v>7.711985779999999</v>
+        <v>7.675981039999999</v>
       </c>
       <c r="O5">
-        <v>1.3881574404</v>
+        <v>1.3816765872</v>
       </c>
       <c r="P5">
-        <v>6.323828339599999</v>
+        <v>6.294304452799999</v>
       </c>
       <c r="Q5">
-        <v>13.1038283396</v>
+        <v>13.0743044528</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.08930952167418513</v>
+        <v>0.08968318327781169</v>
       </c>
       <c r="T5">
-        <v>0.7336330421457906</v>
+        <v>0.7399335135932689</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1723,7 +1723,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>72.39787502052971</v>
+        <v>54.29840626539727</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1731,22 +1731,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.08774569594669922</v>
+        <v>0.0876237758694389</v>
       </c>
       <c r="C6">
-        <v>69.50810537548875</v>
+        <v>68.97266580863389</v>
       </c>
       <c r="D6">
-        <v>61.87130537548876</v>
+        <v>62.05166580863388</v>
       </c>
       <c r="E6">
-        <v>1.7832</v>
+        <v>2.499</v>
       </c>
       <c r="F6">
-        <v>2.8632</v>
+        <v>3.579</v>
       </c>
       <c r="G6">
         <v>10.5</v>
@@ -1767,28 +1767,28 @@
         <v>7.819999999999999</v>
       </c>
       <c r="M6">
-        <v>0.14401896</v>
+        <v>0.1800237</v>
       </c>
       <c r="N6">
-        <v>7.675981039999999</v>
+        <v>7.639976299999999</v>
       </c>
       <c r="O6">
-        <v>1.3816765872</v>
+        <v>1.375195734</v>
       </c>
       <c r="P6">
-        <v>6.294304452799999</v>
+        <v>6.264780565999999</v>
       </c>
       <c r="Q6">
-        <v>13.0743044528</v>
+        <v>13.044780566</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.08968318327781169</v>
+        <v>0.09006471144151462</v>
       </c>
       <c r="T6">
-        <v>0.7399335135932689</v>
+        <v>0.7463666265449046</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1805,7 +1805,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>54.29840626539727</v>
+        <v>43.43872501231782</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1813,22 +1813,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.0876237758694389</v>
+        <v>0.08750185579217856</v>
       </c>
       <c r="C7">
-        <v>68.97266580863389</v>
+        <v>68.43828084990263</v>
       </c>
       <c r="D7">
-        <v>62.05166580863388</v>
+        <v>62.23308084990261</v>
       </c>
       <c r="E7">
-        <v>2.499</v>
+        <v>3.2148</v>
       </c>
       <c r="F7">
-        <v>3.579</v>
+        <v>4.2948</v>
       </c>
       <c r="G7">
         <v>10.5</v>
@@ -1849,28 +1849,28 @@
         <v>7.819999999999999</v>
       </c>
       <c r="M7">
-        <v>0.1800237</v>
+        <v>0.21602844</v>
       </c>
       <c r="N7">
-        <v>7.639976299999999</v>
+        <v>7.60397156</v>
       </c>
       <c r="O7">
-        <v>1.375195734</v>
+        <v>1.3687148808</v>
       </c>
       <c r="P7">
-        <v>6.264780565999999</v>
+        <v>6.2352566792</v>
       </c>
       <c r="Q7">
-        <v>13.044780566</v>
+        <v>13.0152566792</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.09006471144151462</v>
+        <v>0.09045435722572187</v>
       </c>
       <c r="T7">
-        <v>0.7463666265449046</v>
+        <v>0.7529366142401922</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1887,7 +1887,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>43.43872501231782</v>
+        <v>36.19893751026485</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1895,22 +1895,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.08750185579217856</v>
+        <v>0.08737993571491823</v>
       </c>
       <c r="C8">
-        <v>68.43828084990263</v>
+        <v>67.90495977621434</v>
       </c>
       <c r="D8">
-        <v>62.23308084990261</v>
+        <v>62.41555977621434</v>
       </c>
       <c r="E8">
-        <v>3.214799999999999</v>
+        <v>3.930599999999999</v>
       </c>
       <c r="F8">
-        <v>4.2948</v>
+        <v>5.010599999999999</v>
       </c>
       <c r="G8">
         <v>10.5</v>
@@ -1931,28 +1931,28 @@
         <v>7.819999999999999</v>
       </c>
       <c r="M8">
-        <v>0.21602844</v>
+        <v>0.25203318</v>
       </c>
       <c r="N8">
-        <v>7.60397156</v>
+        <v>7.56796682</v>
       </c>
       <c r="O8">
-        <v>1.3687148808</v>
+        <v>1.3622340276</v>
       </c>
       <c r="P8">
-        <v>6.2352566792</v>
+        <v>6.2057327924</v>
       </c>
       <c r="Q8">
-        <v>13.0152566792</v>
+        <v>12.9857327924</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.09045435722572187</v>
+        <v>0.09085238248915939</v>
       </c>
       <c r="T8">
-        <v>0.7529366142401922</v>
+        <v>0.7596478919934431</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1969,7 +1969,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>36.19893751026486</v>
+        <v>31.02766072308416</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1977,22 +1977,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.08737993571491823</v>
+        <v>0.08725801563765791</v>
       </c>
       <c r="C9">
-        <v>67.90495977621434</v>
+        <v>67.37271197361498</v>
       </c>
       <c r="D9">
-        <v>62.41555977621434</v>
+        <v>62.59911197361499</v>
       </c>
       <c r="E9">
-        <v>3.9306</v>
+        <v>4.6464</v>
       </c>
       <c r="F9">
-        <v>5.0106</v>
+        <v>5.7264</v>
       </c>
       <c r="G9">
         <v>10.5</v>
@@ -2013,28 +2013,28 @@
         <v>7.819999999999999</v>
       </c>
       <c r="M9">
-        <v>0.25203318</v>
+        <v>0.28803792</v>
       </c>
       <c r="N9">
-        <v>7.56796682</v>
+        <v>7.53196208</v>
       </c>
       <c r="O9">
-        <v>1.3622340276</v>
+        <v>1.3557531744</v>
       </c>
       <c r="P9">
-        <v>6.2057327924</v>
+        <v>6.176208905599999</v>
       </c>
       <c r="Q9">
-        <v>12.9857327924</v>
+        <v>12.9562089056</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.09085238248915939</v>
+        <v>0.09125906047571511</v>
       </c>
       <c r="T9">
-        <v>0.7596478919934431</v>
+        <v>0.7665050670891559</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2051,7 +2051,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>31.02766072308415</v>
+        <v>27.14920313269864</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2059,22 +2059,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.08725801563765791</v>
+        <v>0.08713609556039757</v>
       </c>
       <c r="C10">
-        <v>67.37271197361498</v>
+        <v>66.84154693888644</v>
       </c>
       <c r="D10">
-        <v>62.59911197361499</v>
+        <v>62.78374693888644</v>
       </c>
       <c r="E10">
-        <v>4.6464</v>
+        <v>5.3622</v>
       </c>
       <c r="F10">
-        <v>5.7264</v>
+        <v>6.4422</v>
       </c>
       <c r="G10">
         <v>10.5</v>
@@ -2095,28 +2095,28 @@
         <v>7.819999999999999</v>
       </c>
       <c r="M10">
-        <v>0.28803792</v>
+        <v>0.32404266</v>
       </c>
       <c r="N10">
-        <v>7.53196208</v>
+        <v>7.495957339999999</v>
       </c>
       <c r="O10">
-        <v>1.3557531744</v>
+        <v>1.3492723212</v>
       </c>
       <c r="P10">
-        <v>6.176208905599999</v>
+        <v>6.1466850188</v>
       </c>
       <c r="Q10">
-        <v>12.9562089056</v>
+        <v>12.9266850188</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.09125906047571511</v>
+        <v>0.09167467643999733</v>
       </c>
       <c r="T10">
-        <v>0.7665050670891559</v>
+        <v>0.7735129493298293</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2133,7 +2133,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>27.14920313269864</v>
+        <v>24.13262500684323</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2141,22 +2141,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.08713609556039757</v>
+        <v>0.08701417548313722</v>
       </c>
       <c r="C11">
-        <v>66.84154693888644</v>
+        <v>66.31147428118435</v>
       </c>
       <c r="D11">
-        <v>62.78374693888644</v>
+        <v>62.96947428118435</v>
       </c>
       <c r="E11">
-        <v>5.3622</v>
+        <v>6.077999999999999</v>
       </c>
       <c r="F11">
-        <v>6.4422</v>
+        <v>7.157999999999999</v>
       </c>
       <c r="G11">
         <v>10.5</v>
@@ -2177,28 +2177,28 @@
         <v>7.819999999999999</v>
       </c>
       <c r="M11">
-        <v>0.32404266</v>
+        <v>0.3600474</v>
       </c>
       <c r="N11">
-        <v>7.495957339999999</v>
+        <v>7.459952599999999</v>
       </c>
       <c r="O11">
-        <v>1.3492723212</v>
+        <v>1.342791468</v>
       </c>
       <c r="P11">
-        <v>6.1466850188</v>
+        <v>6.117161132</v>
       </c>
       <c r="Q11">
-        <v>12.9266850188</v>
+        <v>12.897161132</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.09167467643999733</v>
+        <v>0.09209952831459692</v>
       </c>
       <c r="T11">
-        <v>0.7735129493298293</v>
+        <v>0.7806765622869621</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2215,7 +2215,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>24.13262500684323</v>
+        <v>21.71936250615891</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2223,22 +2223,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.08701417548313724</v>
+        <v>0.0868922554058769</v>
       </c>
       <c r="C12">
-        <v>66.31147428118435</v>
+        <v>65.78250372370519</v>
       </c>
       <c r="D12">
-        <v>62.96947428118434</v>
+        <v>63.15630372370519</v>
       </c>
       <c r="E12">
-        <v>6.078</v>
+        <v>6.7938</v>
       </c>
       <c r="F12">
-        <v>7.158</v>
+        <v>7.8738</v>
       </c>
       <c r="G12">
         <v>10.5</v>
@@ -2259,28 +2259,28 @@
         <v>7.819999999999999</v>
       </c>
       <c r="M12">
-        <v>0.3600474</v>
+        <v>0.39605214</v>
       </c>
       <c r="N12">
-        <v>7.459952599999999</v>
+        <v>7.423947859999999</v>
       </c>
       <c r="O12">
-        <v>1.342791468</v>
+        <v>1.3363106148</v>
       </c>
       <c r="P12">
-        <v>6.117161132</v>
+        <v>6.0876372452</v>
       </c>
       <c r="Q12">
-        <v>12.897161132</v>
+        <v>12.8676372452</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.09209952831459692</v>
+        <v>0.0925339274223336</v>
       </c>
       <c r="T12">
-        <v>0.7806765622869621</v>
+        <v>0.7880011553105475</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2297,7 +2297,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>21.71936250615891</v>
+        <v>19.74487500559901</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2305,22 +2305,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.0868922554058769</v>
+        <v>0.08677033532861657</v>
       </c>
       <c r="C13">
-        <v>65.78250372370519</v>
+        <v>65.25464510538319</v>
       </c>
       <c r="D13">
-        <v>63.15630372370519</v>
+        <v>63.34424510538319</v>
       </c>
       <c r="E13">
-        <v>6.7938</v>
+        <v>7.509599999999999</v>
       </c>
       <c r="F13">
-        <v>7.8738</v>
+        <v>8.589599999999999</v>
       </c>
       <c r="G13">
         <v>10.5</v>
@@ -2341,28 +2341,28 @@
         <v>7.819999999999999</v>
       </c>
       <c r="M13">
-        <v>0.39605214</v>
+        <v>0.4320568799999999</v>
       </c>
       <c r="N13">
-        <v>7.423947859999999</v>
+        <v>7.387943119999999</v>
       </c>
       <c r="O13">
-        <v>1.3363106148</v>
+        <v>1.3298297616</v>
       </c>
       <c r="P13">
-        <v>6.0876372452</v>
+        <v>6.058113358399999</v>
       </c>
       <c r="Q13">
-        <v>12.8676372452</v>
+        <v>12.8381133584</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.0925339274223336</v>
+        <v>0.09297819923706428</v>
       </c>
       <c r="T13">
-        <v>0.7880011553105475</v>
+        <v>0.7954922163573961</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2379,7 +2379,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>19.74487500559901</v>
+        <v>18.09946875513243</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2387,22 +2387,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.08677033532861657</v>
+        <v>0.08664841525135625</v>
       </c>
       <c r="C14">
-        <v>65.25464510538319</v>
+        <v>64.7279083826174</v>
       </c>
       <c r="D14">
-        <v>63.34424510538319</v>
+        <v>63.5333083826174</v>
       </c>
       <c r="E14">
-        <v>7.509599999999999</v>
+        <v>8.2254</v>
       </c>
       <c r="F14">
-        <v>8.589599999999999</v>
+        <v>9.305400000000001</v>
       </c>
       <c r="G14">
         <v>10.5</v>
@@ -2423,28 +2423,28 @@
         <v>7.819999999999999</v>
       </c>
       <c r="M14">
-        <v>0.4320568799999999</v>
+        <v>0.46806162</v>
       </c>
       <c r="N14">
-        <v>7.387943119999999</v>
+        <v>7.351938379999999</v>
       </c>
       <c r="O14">
-        <v>1.3298297616</v>
+        <v>1.3233489084</v>
       </c>
       <c r="P14">
-        <v>6.058113358399999</v>
+        <v>6.028589471599999</v>
       </c>
       <c r="Q14">
-        <v>12.8381133584</v>
+        <v>12.8085894716</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.09297819923706428</v>
+        <v>0.0934326841969612</v>
       </c>
       <c r="T14">
-        <v>0.7954922163573961</v>
+        <v>0.8031554857041724</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2461,7 +2461,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>18.09946875513243</v>
+        <v>16.70720192781454</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2469,22 +2469,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.08664841525135625</v>
+        <v>0.08652649517409591</v>
       </c>
       <c r="C15">
-        <v>64.7279083826174</v>
+        <v>64.20230363103005</v>
       </c>
       <c r="D15">
-        <v>63.5333083826174</v>
+        <v>63.72350363103004</v>
       </c>
       <c r="E15">
-        <v>8.2254</v>
+        <v>8.9412</v>
       </c>
       <c r="F15">
-        <v>9.305400000000001</v>
+        <v>10.0212</v>
       </c>
       <c r="G15">
         <v>10.5</v>
@@ -2505,28 +2505,28 @@
         <v>7.819999999999999</v>
       </c>
       <c r="M15">
-        <v>0.46806162</v>
+        <v>0.50406636</v>
       </c>
       <c r="N15">
-        <v>7.351938379999999</v>
+        <v>7.315933639999999</v>
       </c>
       <c r="O15">
-        <v>1.3233489084</v>
+        <v>1.3168680552</v>
       </c>
       <c r="P15">
-        <v>6.028589471599999</v>
+        <v>5.999065584799999</v>
       </c>
       <c r="Q15">
-        <v>12.8085894716</v>
+        <v>12.7790655848</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.0934326841969612</v>
+        <v>0.09389773857453013</v>
       </c>
       <c r="T15">
-        <v>0.8031554857041724</v>
+        <v>0.8109969706171526</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2543,7 +2543,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>16.70720192781454</v>
+        <v>15.51383036154208</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2551,22 +2551,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.08652649517409591</v>
+        <v>0.08640457509683556</v>
       </c>
       <c r="C16">
-        <v>64.20230363103005</v>
+        <v>63.67784104725634</v>
       </c>
       <c r="D16">
-        <v>63.72350363103004</v>
+        <v>63.91484104725635</v>
       </c>
       <c r="E16">
-        <v>8.9412</v>
+        <v>9.657000000000002</v>
       </c>
       <c r="F16">
-        <v>10.0212</v>
+        <v>10.737</v>
       </c>
       <c r="G16">
         <v>10.5</v>
@@ -2587,28 +2587,28 @@
         <v>7.819999999999999</v>
       </c>
       <c r="M16">
-        <v>0.50406636</v>
+        <v>0.5400711</v>
       </c>
       <c r="N16">
-        <v>7.315933639999999</v>
+        <v>7.2799289</v>
       </c>
       <c r="O16">
-        <v>1.3168680552</v>
+        <v>1.310387202</v>
       </c>
       <c r="P16">
-        <v>5.999065584799999</v>
+        <v>5.969541698</v>
       </c>
       <c r="Q16">
-        <v>12.7790655848</v>
+        <v>12.749541698</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.09389773857453013</v>
+        <v>0.09437373540804185</v>
       </c>
       <c r="T16">
-        <v>0.8109969706171526</v>
+        <v>0.8190229610574971</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -2625,7 +2625,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>15.51383036154208</v>
+        <v>14.47957500410594</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2633,22 +2633,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.08640457509683556</v>
+        <v>0.08628265501957523</v>
       </c>
       <c r="C17">
-        <v>63.67784104725634</v>
+        <v>63.15453095076676</v>
       </c>
       <c r="D17">
-        <v>63.91484104725635</v>
+        <v>64.10733095076675</v>
       </c>
       <c r="E17">
-        <v>9.657</v>
+        <v>10.3728</v>
       </c>
       <c r="F17">
-        <v>10.737</v>
+        <v>11.4528</v>
       </c>
       <c r="G17">
         <v>10.5</v>
@@ -2669,28 +2669,28 @@
         <v>7.819999999999999</v>
       </c>
       <c r="M17">
-        <v>0.5400711</v>
+        <v>0.57607584</v>
       </c>
       <c r="N17">
-        <v>7.2799289</v>
+        <v>7.24392416</v>
       </c>
       <c r="O17">
-        <v>1.310387202</v>
+        <v>1.3039063488</v>
       </c>
       <c r="P17">
-        <v>5.969541698</v>
+        <v>5.9400178112</v>
       </c>
       <c r="Q17">
-        <v>12.749541698</v>
+        <v>12.7200178112</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.09437373540804185</v>
+        <v>0.09486106549949433</v>
       </c>
       <c r="T17">
-        <v>0.8190229610574971</v>
+        <v>0.8272400465083259</v>
       </c>
       <c r="U17">
         <v>0.0503</v>
@@ -2707,7 +2707,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>14.47957500410594</v>
+        <v>13.57460156634932</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2715,22 +2715,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.08628265501957523</v>
+        <v>0.0863698349423149</v>
       </c>
       <c r="C18">
-        <v>63.15453095076676</v>
+        <v>62.30097164838654</v>
       </c>
       <c r="D18">
-        <v>64.10733095076675</v>
+        <v>63.96957164838653</v>
       </c>
       <c r="E18">
-        <v>10.3728</v>
+        <v>11.0886</v>
       </c>
       <c r="F18">
-        <v>11.4528</v>
+        <v>12.1686</v>
       </c>
       <c r="G18">
         <v>10.5</v>
@@ -2751,45 +2751,45 @@
         <v>7.819999999999999</v>
       </c>
       <c r="M18">
-        <v>0.57607584</v>
+        <v>0.6303334800000001</v>
       </c>
       <c r="N18">
-        <v>7.24392416</v>
+        <v>7.189666519999999</v>
       </c>
       <c r="O18">
-        <v>1.3039063488</v>
+        <v>1.2941399736</v>
       </c>
       <c r="P18">
-        <v>5.9400178112</v>
+        <v>5.895526546399999</v>
       </c>
       <c r="Q18">
-        <v>12.7200178112</v>
+        <v>12.6755265464</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.09486106549949433</v>
+        <v>0.09536013848471675</v>
       </c>
       <c r="T18">
-        <v>0.8272400465083259</v>
+        <v>0.8356551340182109</v>
       </c>
       <c r="U18">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V18">
         <v>0.18</v>
       </c>
       <c r="W18">
-        <v>0.041246</v>
+        <v>0.042476</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y18">
-        <v>13.57460156634932</v>
+        <v>12.40613143379279</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2797,22 +2797,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.0863698349423149</v>
+        <v>0.08626021486505457</v>
       </c>
       <c r="C19">
-        <v>62.30097164838654</v>
+        <v>61.75848633318972</v>
       </c>
       <c r="D19">
-        <v>63.96957164838653</v>
+        <v>64.14288633318972</v>
       </c>
       <c r="E19">
-        <v>11.0886</v>
+        <v>11.8044</v>
       </c>
       <c r="F19">
-        <v>12.1686</v>
+        <v>12.8844</v>
       </c>
       <c r="G19">
         <v>10.5</v>
@@ -2833,28 +2833,28 @@
         <v>7.819999999999999</v>
       </c>
       <c r="M19">
-        <v>0.6303334800000001</v>
+        <v>0.66741192</v>
       </c>
       <c r="N19">
-        <v>7.189666519999999</v>
+        <v>7.152588079999999</v>
       </c>
       <c r="O19">
-        <v>1.2941399736</v>
+        <v>1.2874658544</v>
       </c>
       <c r="P19">
-        <v>5.895526546399999</v>
+        <v>5.8651222256</v>
       </c>
       <c r="Q19">
-        <v>12.6755265464</v>
+        <v>12.6451222256</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.09536013848471675</v>
+        <v>0.09587138398177387</v>
       </c>
       <c r="T19">
-        <v>0.8356551340182109</v>
+        <v>0.8442754675649226</v>
       </c>
       <c r="U19">
         <v>0.0518</v>
@@ -2871,7 +2871,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>12.40613143379279</v>
+        <v>11.71690190969319</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2879,22 +2879,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.08626021486505457</v>
+        <v>0.08615059478779424</v>
       </c>
       <c r="C20">
-        <v>61.75848633318972</v>
+        <v>61.21694270270602</v>
       </c>
       <c r="D20">
-        <v>64.14288633318972</v>
+        <v>64.31714270270602</v>
       </c>
       <c r="E20">
-        <v>11.8044</v>
+        <v>12.5202</v>
       </c>
       <c r="F20">
-        <v>12.8844</v>
+        <v>13.6002</v>
       </c>
       <c r="G20">
         <v>10.5</v>
@@ -2915,28 +2915,28 @@
         <v>7.819999999999999</v>
       </c>
       <c r="M20">
-        <v>0.6674119199999999</v>
+        <v>0.70449036</v>
       </c>
       <c r="N20">
-        <v>7.152588079999999</v>
+        <v>7.115509639999999</v>
       </c>
       <c r="O20">
-        <v>1.2874658544</v>
+        <v>1.2807917352</v>
       </c>
       <c r="P20">
-        <v>5.8651222256</v>
+        <v>5.8347179048</v>
       </c>
       <c r="Q20">
-        <v>12.6451222256</v>
+        <v>12.6147179048</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.09587138398177386</v>
+        <v>0.09639525282443734</v>
       </c>
       <c r="T20">
-        <v>0.8442754675649223</v>
+        <v>0.853108648853528</v>
       </c>
       <c r="U20">
         <v>0.0518</v>
@@ -2953,7 +2953,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>11.71690190969319</v>
+        <v>11.1002228618146</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2961,22 +2961,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.08615059478779424</v>
+        <v>0.0860409747105339</v>
       </c>
       <c r="C21">
-        <v>61.21694270270602</v>
+        <v>60.67634845264004</v>
       </c>
       <c r="D21">
-        <v>64.31714270270602</v>
+        <v>64.49234845264004</v>
       </c>
       <c r="E21">
-        <v>12.5202</v>
+        <v>13.236</v>
       </c>
       <c r="F21">
-        <v>13.6002</v>
+        <v>14.316</v>
       </c>
       <c r="G21">
         <v>10.5</v>
@@ -2997,28 +2997,28 @@
         <v>7.819999999999999</v>
       </c>
       <c r="M21">
-        <v>0.70449036</v>
+        <v>0.7415688</v>
       </c>
       <c r="N21">
-        <v>7.115509639999999</v>
+        <v>7.078431199999999</v>
       </c>
       <c r="O21">
-        <v>1.2807917352</v>
+        <v>1.274117616</v>
       </c>
       <c r="P21">
-        <v>5.8347179048</v>
+        <v>5.804313583999999</v>
       </c>
       <c r="Q21">
-        <v>12.6147179048</v>
+        <v>12.584313584</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.09639525282443734</v>
+        <v>0.09693221838816737</v>
       </c>
       <c r="T21">
-        <v>0.853108648853528</v>
+        <v>0.8621626596743488</v>
       </c>
       <c r="U21">
         <v>0.0518</v>
@@ -3035,7 +3035,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>11.1002228618146</v>
+        <v>10.54521171872387</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3043,22 +3043,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.0860409747105339</v>
+        <v>0.08593135463327357</v>
       </c>
       <c r="C22">
-        <v>60.67634845264004</v>
+        <v>60.13671136278056</v>
       </c>
       <c r="D22">
-        <v>64.49234845264004</v>
+        <v>64.66851136278056</v>
       </c>
       <c r="E22">
-        <v>13.236</v>
+        <v>13.9518</v>
       </c>
       <c r="F22">
-        <v>14.316</v>
+        <v>15.0318</v>
       </c>
       <c r="G22">
         <v>10.5</v>
@@ -3079,28 +3079,28 @@
         <v>7.819999999999999</v>
       </c>
       <c r="M22">
-        <v>0.7415688</v>
+        <v>0.77864724</v>
       </c>
       <c r="N22">
-        <v>7.078431199999999</v>
+        <v>7.04135276</v>
       </c>
       <c r="O22">
-        <v>1.274117616</v>
+        <v>1.2674434968</v>
       </c>
       <c r="P22">
-        <v>5.804313583999999</v>
+        <v>5.7739092632</v>
       </c>
       <c r="Q22">
-        <v>12.584313584</v>
+        <v>12.5539092632</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.09693221838816737</v>
+        <v>0.09748277801680198</v>
       </c>
       <c r="T22">
-        <v>0.8621626596743488</v>
+        <v>0.8714458859589876</v>
       </c>
       <c r="U22">
         <v>0.0518</v>
@@ -3117,7 +3117,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>10.54521171872387</v>
+        <v>10.04305877973702</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3125,22 +3125,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.08593135463327357</v>
+        <v>0.08612841455601325</v>
       </c>
       <c r="C23">
-        <v>60.13671136278057</v>
+        <v>59.10491649927956</v>
       </c>
       <c r="D23">
-        <v>64.66851136278056</v>
+        <v>64.35251649927956</v>
       </c>
       <c r="E23">
-        <v>13.9518</v>
+        <v>14.6676</v>
       </c>
       <c r="F23">
-        <v>15.0318</v>
+        <v>15.7476</v>
       </c>
       <c r="G23">
         <v>10.5</v>
@@ -3161,45 +3161,45 @@
         <v>7.819999999999999</v>
       </c>
       <c r="M23">
-        <v>0.77864724</v>
+        <v>0.8424966</v>
       </c>
       <c r="N23">
-        <v>7.04135276</v>
+        <v>6.9775034</v>
       </c>
       <c r="O23">
-        <v>1.2674434968</v>
+        <v>1.255950612</v>
       </c>
       <c r="P23">
-        <v>5.7739092632</v>
+        <v>5.721552788</v>
       </c>
       <c r="Q23">
-        <v>12.5539092632</v>
+        <v>12.501552788</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.09748277801680198</v>
+        <v>0.09804745455899133</v>
       </c>
       <c r="T23">
-        <v>0.8714458859589876</v>
+        <v>0.8809671436868226</v>
       </c>
       <c r="U23">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V23">
         <v>0.18</v>
       </c>
       <c r="W23">
-        <v>0.042476</v>
+        <v>0.04387</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y23">
-        <v>10.04305877973702</v>
+        <v>9.281936568052618</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3207,22 +3207,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.08612841455601325</v>
+        <v>0.08603273447875291</v>
       </c>
       <c r="C24">
-        <v>59.10491649927956</v>
+        <v>58.54215739571178</v>
       </c>
       <c r="D24">
-        <v>64.35251649927956</v>
+        <v>64.50555739571178</v>
       </c>
       <c r="E24">
-        <v>14.6676</v>
+        <v>15.3834</v>
       </c>
       <c r="F24">
-        <v>15.7476</v>
+        <v>16.4634</v>
       </c>
       <c r="G24">
         <v>10.5</v>
@@ -3243,28 +3243,28 @@
         <v>7.819999999999999</v>
       </c>
       <c r="M24">
-        <v>0.8424966</v>
+        <v>0.8807919</v>
       </c>
       <c r="N24">
-        <v>6.9775034</v>
+        <v>6.939208099999999</v>
       </c>
       <c r="O24">
-        <v>1.255950612</v>
+        <v>1.249057458</v>
       </c>
       <c r="P24">
-        <v>5.721552788</v>
+        <v>5.690150641999999</v>
       </c>
       <c r="Q24">
-        <v>12.501552788</v>
+        <v>12.470150642</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.09804745455899133</v>
+        <v>0.09862679802435442</v>
       </c>
       <c r="T24">
-        <v>0.8809671436868226</v>
+        <v>0.8907357068101857</v>
       </c>
       <c r="U24">
         <v>0.0535</v>
@@ -3281,7 +3281,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>9.281936568052618</v>
+        <v>8.87837410857207</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3289,22 +3289,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.08603273447875291</v>
+        <v>0.08593705440149257</v>
       </c>
       <c r="C25">
-        <v>58.54215739571178</v>
+        <v>57.9801279403463</v>
       </c>
       <c r="D25">
-        <v>64.50555739571178</v>
+        <v>64.6593279403463</v>
       </c>
       <c r="E25">
-        <v>15.3834</v>
+        <v>16.0992</v>
       </c>
       <c r="F25">
-        <v>16.4634</v>
+        <v>17.1792</v>
       </c>
       <c r="G25">
         <v>10.5</v>
@@ -3325,28 +3325,28 @@
         <v>7.819999999999999</v>
       </c>
       <c r="M25">
-        <v>0.8807919</v>
+        <v>0.9190872000000001</v>
       </c>
       <c r="N25">
-        <v>6.939208099999999</v>
+        <v>6.9009128</v>
       </c>
       <c r="O25">
-        <v>1.249057458</v>
+        <v>1.242164304</v>
       </c>
       <c r="P25">
-        <v>5.690150641999999</v>
+        <v>5.658748495999999</v>
       </c>
       <c r="Q25">
-        <v>12.470150642</v>
+        <v>12.438748496</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.09862679802435442</v>
+        <v>0.09922138737038497</v>
       </c>
       <c r="T25">
-        <v>0.8907357068101857</v>
+        <v>0.9007613373841635</v>
       </c>
       <c r="U25">
         <v>0.0535</v>
@@ -3363,7 +3363,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>8.87837410857207</v>
+        <v>8.508441854048232</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3371,22 +3371,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.08593705440149257</v>
+        <v>0.08584137432423225</v>
       </c>
       <c r="C26">
-        <v>57.98012794034631</v>
+        <v>57.41883336373256</v>
       </c>
       <c r="D26">
-        <v>64.6593279403463</v>
+        <v>64.81383336373256</v>
       </c>
       <c r="E26">
-        <v>16.0992</v>
+        <v>16.815</v>
       </c>
       <c r="F26">
-        <v>17.1792</v>
+        <v>17.895</v>
       </c>
       <c r="G26">
         <v>10.5</v>
@@ -3407,28 +3407,28 @@
         <v>7.819999999999999</v>
       </c>
       <c r="M26">
-        <v>0.9190871999999999</v>
+        <v>0.9573824999999999</v>
       </c>
       <c r="N26">
-        <v>6.9009128</v>
+        <v>6.8626175</v>
       </c>
       <c r="O26">
-        <v>1.242164304</v>
+        <v>1.23527115</v>
       </c>
       <c r="P26">
-        <v>5.658748495999999</v>
+        <v>5.62734635</v>
       </c>
       <c r="Q26">
-        <v>12.438748496</v>
+        <v>12.40734635</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.09922138737038497</v>
+        <v>0.09983183243230966</v>
       </c>
       <c r="T26">
-        <v>0.9007613373841634</v>
+        <v>0.9110543181067807</v>
       </c>
       <c r="U26">
         <v>0.0535</v>
@@ -3445,7 +3445,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>8.508441854048234</v>
+        <v>8.168104179886306</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3453,22 +3453,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.08584137432423225</v>
+        <v>0.08574569424697191</v>
       </c>
       <c r="C27">
-        <v>57.41883336373256</v>
+        <v>56.85827894653403</v>
       </c>
       <c r="D27">
-        <v>64.81383336373256</v>
+        <v>64.96907894653403</v>
       </c>
       <c r="E27">
-        <v>16.815</v>
+        <v>17.5308</v>
       </c>
       <c r="F27">
-        <v>17.895</v>
+        <v>18.6108</v>
       </c>
       <c r="G27">
         <v>10.5</v>
@@ -3489,28 +3489,28 @@
         <v>7.819999999999999</v>
       </c>
       <c r="M27">
-        <v>0.9573824999999999</v>
+        <v>0.9956778000000001</v>
       </c>
       <c r="N27">
-        <v>6.8626175</v>
+        <v>6.824322199999999</v>
       </c>
       <c r="O27">
-        <v>1.23527115</v>
+        <v>1.228377996</v>
       </c>
       <c r="P27">
-        <v>5.62734635</v>
+        <v>5.595944203999999</v>
       </c>
       <c r="Q27">
-        <v>12.40734635</v>
+        <v>12.375944204</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.09983183243230966</v>
+        <v>0.1004587760094215</v>
       </c>
       <c r="T27">
-        <v>0.9110543181067807</v>
+        <v>0.9216254874975768</v>
       </c>
       <c r="U27">
         <v>0.0535</v>
@@ -3527,7 +3527,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>8.168104179886306</v>
+        <v>7.853946326813753</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3535,22 +3535,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.08574569424697191</v>
+        <v>0.08582713416971158</v>
       </c>
       <c r="C28">
-        <v>56.85827894653403</v>
+        <v>56.01029169706872</v>
       </c>
       <c r="D28">
-        <v>64.96907894653403</v>
+        <v>64.83689169706872</v>
       </c>
       <c r="E28">
-        <v>17.5308</v>
+        <v>18.2466</v>
       </c>
       <c r="F28">
-        <v>18.6108</v>
+        <v>19.3266</v>
       </c>
       <c r="G28">
         <v>10.5</v>
@@ -3571,45 +3571,45 @@
         <v>7.819999999999999</v>
       </c>
       <c r="M28">
-        <v>0.9956778000000001</v>
+        <v>1.04943438</v>
       </c>
       <c r="N28">
-        <v>6.824322199999999</v>
+        <v>6.770565619999999</v>
       </c>
       <c r="O28">
-        <v>1.228377996</v>
+        <v>1.2187018116</v>
       </c>
       <c r="P28">
-        <v>5.595944203999999</v>
+        <v>5.551863808399999</v>
       </c>
       <c r="Q28">
-        <v>12.375944204</v>
+        <v>12.3318638084</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1004587760094215</v>
+        <v>0.1011028961228926</v>
       </c>
       <c r="T28">
-        <v>0.9216254874975768</v>
+        <v>0.9324862779675728</v>
       </c>
       <c r="U28">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V28">
         <v>0.18</v>
       </c>
       <c r="W28">
-        <v>0.04387</v>
+        <v>0.044526</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y28">
-        <v>7.853946326813753</v>
+        <v>7.451633135937475</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3617,22 +3617,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.08582713416971158</v>
+        <v>0.08573801409245124</v>
       </c>
       <c r="C29">
-        <v>56.01029169706872</v>
+        <v>55.43917262146289</v>
       </c>
       <c r="D29">
-        <v>64.83689169706872</v>
+        <v>64.98157262146289</v>
       </c>
       <c r="E29">
-        <v>18.2466</v>
+        <v>18.9624</v>
       </c>
       <c r="F29">
-        <v>19.3266</v>
+        <v>20.0424</v>
       </c>
       <c r="G29">
         <v>10.5</v>
@@ -3653,28 +3653,28 @@
         <v>7.819999999999999</v>
       </c>
       <c r="M29">
-        <v>1.04943438</v>
+        <v>1.08830232</v>
       </c>
       <c r="N29">
-        <v>6.770565619999999</v>
+        <v>6.731697679999999</v>
       </c>
       <c r="O29">
-        <v>1.2187018116</v>
+        <v>1.2117055824</v>
       </c>
       <c r="P29">
-        <v>5.551863808399999</v>
+        <v>5.519992097599999</v>
       </c>
       <c r="Q29">
-        <v>12.3318638084</v>
+        <v>12.2999920976</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1011028961228926</v>
+        <v>0.1017649084617378</v>
       </c>
       <c r="T29">
-        <v>0.9324862779675728</v>
+        <v>0.9436487570617355</v>
       </c>
       <c r="U29">
         <v>0.0543</v>
@@ -3691,7 +3691,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>7.451633135937475</v>
+        <v>7.185503381082563</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3699,22 +3699,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.08573801409245124</v>
+        <v>0.08564889401519091</v>
       </c>
       <c r="C30">
-        <v>55.43917262146289</v>
+        <v>54.8687006892962</v>
       </c>
       <c r="D30">
-        <v>64.98157262146289</v>
+        <v>65.12690068929621</v>
       </c>
       <c r="E30">
-        <v>18.9624</v>
+        <v>19.6782</v>
       </c>
       <c r="F30">
-        <v>20.0424</v>
+        <v>20.7582</v>
       </c>
       <c r="G30">
         <v>10.5</v>
@@ -3735,28 +3735,28 @@
         <v>7.819999999999999</v>
       </c>
       <c r="M30">
-        <v>1.08830232</v>
+        <v>1.12717026</v>
       </c>
       <c r="N30">
-        <v>6.731697679999999</v>
+        <v>6.692829739999999</v>
       </c>
       <c r="O30">
-        <v>1.2117055824</v>
+        <v>1.2047093532</v>
       </c>
       <c r="P30">
-        <v>5.519992097599999</v>
+        <v>5.488120386799999</v>
       </c>
       <c r="Q30">
-        <v>12.2999920976</v>
+        <v>12.2681203868</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1017649084617378</v>
+        <v>0.1024455690354801</v>
       </c>
       <c r="T30">
-        <v>0.9436487570617355</v>
+        <v>0.9551256721867193</v>
       </c>
       <c r="U30">
         <v>0.0543</v>
@@ -3773,7 +3773,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>7.185503381082563</v>
+        <v>6.937727402424544</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3781,22 +3781,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.08564889401519091</v>
+        <v>0.08555977393793057</v>
       </c>
       <c r="C31">
-        <v>54.8687006892962</v>
+        <v>54.29888025221368</v>
       </c>
       <c r="D31">
-        <v>65.12690068929621</v>
+        <v>65.27288025221368</v>
       </c>
       <c r="E31">
-        <v>19.6782</v>
+        <v>20.394</v>
       </c>
       <c r="F31">
-        <v>20.7582</v>
+        <v>21.474</v>
       </c>
       <c r="G31">
         <v>10.5</v>
@@ -3817,28 +3817,28 @@
         <v>7.819999999999999</v>
       </c>
       <c r="M31">
-        <v>1.12717026</v>
+        <v>1.1660382</v>
       </c>
       <c r="N31">
-        <v>6.69282974</v>
+        <v>6.653961799999999</v>
       </c>
       <c r="O31">
-        <v>1.2047093532</v>
+        <v>1.197713124</v>
       </c>
       <c r="P31">
-        <v>5.488120386799999</v>
+        <v>5.456248676</v>
       </c>
       <c r="Q31">
-        <v>12.2681203868</v>
+        <v>12.236248676</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1024455690354801</v>
+        <v>0.1031456770541865</v>
       </c>
       <c r="T31">
-        <v>0.9551256721867193</v>
+        <v>0.9669304991724172</v>
       </c>
       <c r="U31">
         <v>0.0543</v>
@@ -3855,7 +3855,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>6.937727402424546</v>
+        <v>6.706469822343727</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3863,22 +3863,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.08555977393793057</v>
+        <v>0.08547065386067024</v>
       </c>
       <c r="C32">
-        <v>54.29888025221368</v>
+        <v>53.72971570096409</v>
       </c>
       <c r="D32">
-        <v>65.27288025221368</v>
+        <v>65.41951570096408</v>
       </c>
       <c r="E32">
-        <v>20.394</v>
+        <v>21.1098</v>
       </c>
       <c r="F32">
-        <v>21.474</v>
+        <v>22.1898</v>
       </c>
       <c r="G32">
         <v>10.5</v>
@@ -3899,28 +3899,28 @@
         <v>7.819999999999999</v>
       </c>
       <c r="M32">
-        <v>1.1660382</v>
+        <v>1.20490614</v>
       </c>
       <c r="N32">
-        <v>6.653961799999999</v>
+        <v>6.61509386</v>
       </c>
       <c r="O32">
-        <v>1.197713124</v>
+        <v>1.1907168948</v>
       </c>
       <c r="P32">
-        <v>5.456248676</v>
+        <v>5.4243769652</v>
       </c>
       <c r="Q32">
-        <v>12.236248676</v>
+        <v>12.2043769652</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1031456770541865</v>
+        <v>0.1038660780589424</v>
       </c>
       <c r="T32">
-        <v>0.9669304991724172</v>
+        <v>0.9790774950562513</v>
       </c>
       <c r="U32">
         <v>0.0543</v>
@@ -3937,7 +3937,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>6.706469822343727</v>
+        <v>6.490132086139092</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3945,22 +3945,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.08547065386067024</v>
+        <v>0.0853815337834099</v>
       </c>
       <c r="C33">
-        <v>53.72971570096409</v>
+        <v>53.16121146584036</v>
       </c>
       <c r="D33">
-        <v>65.41951570096408</v>
+        <v>65.56681146584036</v>
       </c>
       <c r="E33">
-        <v>21.1098</v>
+        <v>21.8256</v>
       </c>
       <c r="F33">
-        <v>22.1898</v>
+        <v>22.9056</v>
       </c>
       <c r="G33">
         <v>10.5</v>
@@ -3981,28 +3981,28 @@
         <v>7.819999999999999</v>
       </c>
       <c r="M33">
-        <v>1.20490614</v>
+        <v>1.24377408</v>
       </c>
       <c r="N33">
-        <v>6.61509386</v>
+        <v>6.576225919999999</v>
       </c>
       <c r="O33">
-        <v>1.1907168948</v>
+        <v>1.1837206656</v>
       </c>
       <c r="P33">
-        <v>5.4243769652</v>
+        <v>5.3925052544</v>
       </c>
       <c r="Q33">
-        <v>12.2043769652</v>
+        <v>12.1725052544</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1038660780589424</v>
+        <v>0.104607667328544</v>
       </c>
       <c r="T33">
-        <v>0.9790774950562513</v>
+        <v>0.991581755524904</v>
       </c>
       <c r="U33">
         <v>0.0543</v>
@@ -4019,7 +4019,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>6.490132086139092</v>
+        <v>6.287315458447243</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4027,22 +4027,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.0853815337834099</v>
+        <v>0.08556301370614958</v>
       </c>
       <c r="C34">
-        <v>53.16121146584036</v>
+        <v>52.14616201842569</v>
       </c>
       <c r="D34">
-        <v>65.56681146584036</v>
+        <v>65.26756201842569</v>
       </c>
       <c r="E34">
-        <v>21.8256</v>
+        <v>22.5414</v>
       </c>
       <c r="F34">
-        <v>22.9056</v>
+        <v>23.6214</v>
       </c>
       <c r="G34">
         <v>10.5</v>
@@ -4063,45 +4063,45 @@
         <v>7.819999999999999</v>
       </c>
       <c r="M34">
-        <v>1.24377408</v>
+        <v>1.30626342</v>
       </c>
       <c r="N34">
-        <v>6.576225919999999</v>
+        <v>6.51373658</v>
       </c>
       <c r="O34">
-        <v>1.1837206656</v>
+        <v>1.1724725844</v>
       </c>
       <c r="P34">
-        <v>5.3925052544</v>
+        <v>5.3412639956</v>
       </c>
       <c r="Q34">
-        <v>12.1725052544</v>
+        <v>12.1212639956</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.104607667328544</v>
+        <v>0.105371393591268</v>
       </c>
       <c r="T34">
-        <v>0.991581755524904</v>
+        <v>1.004459277500084</v>
       </c>
       <c r="U34">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V34">
         <v>0.18</v>
       </c>
       <c r="W34">
-        <v>0.044526</v>
+        <v>0.045346</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y34">
-        <v>6.287315458447243</v>
+        <v>5.986541366977879</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4109,22 +4109,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.08556301370614958</v>
+        <v>0.08548209362888923</v>
       </c>
       <c r="C35">
-        <v>52.14616201842569</v>
+        <v>51.56345620973823</v>
       </c>
       <c r="D35">
-        <v>65.26756201842569</v>
+        <v>65.40065620973823</v>
       </c>
       <c r="E35">
-        <v>22.5414</v>
+        <v>23.2572</v>
       </c>
       <c r="F35">
-        <v>23.6214</v>
+        <v>24.3372</v>
       </c>
       <c r="G35">
         <v>10.5</v>
@@ -4145,28 +4145,28 @@
         <v>7.819999999999999</v>
       </c>
       <c r="M35">
-        <v>1.30626342</v>
+        <v>1.34584716</v>
       </c>
       <c r="N35">
-        <v>6.51373658</v>
+        <v>6.474152839999999</v>
       </c>
       <c r="O35">
-        <v>1.1724725844</v>
+        <v>1.1653475112</v>
       </c>
       <c r="P35">
-        <v>5.3412639956</v>
+        <v>5.3088053288</v>
       </c>
       <c r="Q35">
-        <v>12.1212639956</v>
+        <v>12.0888053288</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.105371393591268</v>
+        <v>0.1061582630740746</v>
       </c>
       <c r="T35">
-        <v>1.004459277500084</v>
+        <v>1.017727027413905</v>
       </c>
       <c r="U35">
         <v>0.0553</v>
@@ -4183,7 +4183,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>5.986541366977879</v>
+        <v>5.810466620890294</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4191,22 +4191,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.08548209362888923</v>
+        <v>0.08540117355162891</v>
       </c>
       <c r="C36">
-        <v>51.56345620973823</v>
+        <v>50.98129432393372</v>
       </c>
       <c r="D36">
-        <v>65.40065620973823</v>
+        <v>65.53429432393372</v>
       </c>
       <c r="E36">
-        <v>23.2572</v>
+        <v>23.973</v>
       </c>
       <c r="F36">
-        <v>24.3372</v>
+        <v>25.053</v>
       </c>
       <c r="G36">
         <v>10.5</v>
@@ -4227,28 +4227,28 @@
         <v>7.819999999999999</v>
       </c>
       <c r="M36">
-        <v>1.34584716</v>
+        <v>1.3854309</v>
       </c>
       <c r="N36">
-        <v>6.474152839999999</v>
+        <v>6.434569099999999</v>
       </c>
       <c r="O36">
-        <v>1.1653475112</v>
+        <v>1.158222438</v>
       </c>
       <c r="P36">
-        <v>5.3088053288</v>
+        <v>5.276346661999999</v>
       </c>
       <c r="Q36">
-        <v>12.0888053288</v>
+        <v>12.056346662</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1061582630740746</v>
+        <v>0.1069693439255829</v>
       </c>
       <c r="T36">
-        <v>1.017727027413905</v>
+        <v>1.031403015786613</v>
       </c>
       <c r="U36">
         <v>0.0553</v>
@@ -4265,7 +4265,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>5.810466620890294</v>
+        <v>5.644453288864857</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4273,22 +4273,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.08540117355162891</v>
+        <v>0.08532025347436857</v>
       </c>
       <c r="C37">
-        <v>50.98129432393372</v>
+        <v>50.39967970215589</v>
       </c>
       <c r="D37">
-        <v>65.53429432393372</v>
+        <v>65.66847970215589</v>
       </c>
       <c r="E37">
-        <v>23.973</v>
+        <v>24.6888</v>
       </c>
       <c r="F37">
-        <v>25.053</v>
+        <v>25.7688</v>
       </c>
       <c r="G37">
         <v>10.5</v>
@@ -4309,28 +4309,28 @@
         <v>7.819999999999999</v>
       </c>
       <c r="M37">
-        <v>1.3854309</v>
+        <v>1.42501464</v>
       </c>
       <c r="N37">
-        <v>6.434569099999999</v>
+        <v>6.39498536</v>
       </c>
       <c r="O37">
-        <v>1.158222438</v>
+        <v>1.1510973648</v>
       </c>
       <c r="P37">
-        <v>5.276346661999999</v>
+        <v>5.2438879952</v>
       </c>
       <c r="Q37">
-        <v>12.056346662</v>
+        <v>12.0238879952</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1069693439255829</v>
+        <v>0.1078057710537009</v>
       </c>
       <c r="T37">
-        <v>1.031403015786613</v>
+        <v>1.045506378795969</v>
       </c>
       <c r="U37">
         <v>0.0553</v>
@@ -4347,7 +4347,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>5.644453288864857</v>
+        <v>5.487662919729722</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4355,22 +4355,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.08532025347436858</v>
+        <v>0.08523933339710825</v>
       </c>
       <c r="C38">
-        <v>50.39967970215588</v>
+        <v>49.8186157129693</v>
       </c>
       <c r="D38">
-        <v>65.66847970215588</v>
+        <v>65.8032157129693</v>
       </c>
       <c r="E38">
-        <v>24.6888</v>
+        <v>25.4046</v>
       </c>
       <c r="F38">
-        <v>25.7688</v>
+        <v>26.4846</v>
       </c>
       <c r="G38">
         <v>10.5</v>
@@ -4391,28 +4391,28 @@
         <v>7.819999999999999</v>
       </c>
       <c r="M38">
-        <v>1.42501464</v>
+        <v>1.46459838</v>
       </c>
       <c r="N38">
-        <v>6.39498536</v>
+        <v>6.355401619999999</v>
       </c>
       <c r="O38">
-        <v>1.1510973648</v>
+        <v>1.1439722916</v>
       </c>
       <c r="P38">
-        <v>5.2438879952</v>
+        <v>5.2114293284</v>
       </c>
       <c r="Q38">
-        <v>12.0238879952</v>
+        <v>11.9914293284</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1078057710537009</v>
+        <v>0.1086687514239813</v>
       </c>
       <c r="T38">
-        <v>1.045506378795969</v>
+        <v>1.060057467615145</v>
       </c>
       <c r="U38">
         <v>0.0553</v>
@@ -4429,7 +4429,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>5.487662919729723</v>
+        <v>5.339347705682973</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4437,22 +4437,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.08523933339710825</v>
+        <v>0.08515841331984791</v>
       </c>
       <c r="C39">
-        <v>49.8186157129693</v>
+        <v>49.23810575264136</v>
       </c>
       <c r="D39">
-        <v>65.8032157129693</v>
+        <v>65.93850575264136</v>
       </c>
       <c r="E39">
-        <v>25.4046</v>
+        <v>26.1204</v>
       </c>
       <c r="F39">
-        <v>26.4846</v>
+        <v>27.2004</v>
       </c>
       <c r="G39">
         <v>10.5</v>
@@ -4473,28 +4473,28 @@
         <v>7.819999999999999</v>
       </c>
       <c r="M39">
-        <v>1.46459838</v>
+        <v>1.50418212</v>
       </c>
       <c r="N39">
-        <v>6.355401619999999</v>
+        <v>6.315817879999999</v>
       </c>
       <c r="O39">
-        <v>1.1439722916</v>
+        <v>1.1368472184</v>
       </c>
       <c r="P39">
-        <v>5.2114293284</v>
+        <v>5.178970661599999</v>
       </c>
       <c r="Q39">
-        <v>11.9914293284</v>
+        <v>11.9589706616</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1086687514239813</v>
+        <v>0.1095595698707224</v>
       </c>
       <c r="T39">
-        <v>1.060057467615145</v>
+        <v>1.07507794639623</v>
       </c>
       <c r="U39">
         <v>0.0553</v>
@@ -4511,7 +4511,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>5.339347705682973</v>
+        <v>5.198838555533421</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4519,22 +4519,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.08515841331984791</v>
+        <v>0.08507749324258759</v>
       </c>
       <c r="C40">
-        <v>49.23810575264136</v>
+        <v>48.6581532454276</v>
       </c>
       <c r="D40">
-        <v>65.93850575264136</v>
+        <v>66.0743532454276</v>
       </c>
       <c r="E40">
-        <v>26.1204</v>
+        <v>26.8362</v>
       </c>
       <c r="F40">
-        <v>27.2004</v>
+        <v>27.9162</v>
       </c>
       <c r="G40">
         <v>10.5</v>
@@ -4555,28 +4555,28 @@
         <v>7.819999999999999</v>
       </c>
       <c r="M40">
-        <v>1.50418212</v>
+        <v>1.54376586</v>
       </c>
       <c r="N40">
-        <v>6.315817879999999</v>
+        <v>6.27623414</v>
       </c>
       <c r="O40">
-        <v>1.1368472184</v>
+        <v>1.1297221452</v>
       </c>
       <c r="P40">
-        <v>5.178970661599999</v>
+        <v>5.1465119948</v>
       </c>
       <c r="Q40">
-        <v>11.9589706616</v>
+        <v>11.9265119948</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1095595698707224</v>
+        <v>0.1104795954796518</v>
       </c>
       <c r="T40">
-        <v>1.07507794639623</v>
+        <v>1.090590899891449</v>
       </c>
       <c r="U40">
         <v>0.0553</v>
@@ -4593,7 +4593,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>5.198838555533421</v>
+        <v>5.065535002827436</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4601,22 +4601,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.08507749324258759</v>
+        <v>0.08499657316532724</v>
       </c>
       <c r="C41">
-        <v>48.6581532454276</v>
+        <v>48.07876164386069</v>
       </c>
       <c r="D41">
-        <v>66.0743532454276</v>
+        <v>66.21076164386069</v>
       </c>
       <c r="E41">
-        <v>26.8362</v>
+        <v>27.552</v>
       </c>
       <c r="F41">
-        <v>27.9162</v>
+        <v>28.632</v>
       </c>
       <c r="G41">
         <v>10.5</v>
@@ -4637,28 +4637,28 @@
         <v>7.819999999999999</v>
       </c>
       <c r="M41">
-        <v>1.54376586</v>
+        <v>1.5833496</v>
       </c>
       <c r="N41">
-        <v>6.27623414</v>
+        <v>6.236650399999999</v>
       </c>
       <c r="O41">
-        <v>1.1297221452</v>
+        <v>1.122597072</v>
       </c>
       <c r="P41">
-        <v>5.1465119948</v>
+        <v>5.114053328</v>
       </c>
       <c r="Q41">
-        <v>11.9265119948</v>
+        <v>11.894053328</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1104795954796518</v>
+        <v>0.1114302886088787</v>
       </c>
       <c r="T41">
-        <v>1.090590899891449</v>
+        <v>1.106620951836509</v>
       </c>
       <c r="U41">
         <v>0.0553</v>
@@ -4675,7 +4675,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>5.065535002827436</v>
+        <v>4.938896627756749</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4683,22 +4683,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.08499657316532724</v>
+        <v>0.08491565308806691</v>
       </c>
       <c r="C42">
-        <v>48.07876164386069</v>
+        <v>47.49993442904272</v>
       </c>
       <c r="D42">
-        <v>66.21076164386069</v>
+        <v>66.34773442904273</v>
       </c>
       <c r="E42">
-        <v>27.552</v>
+        <v>28.2678</v>
       </c>
       <c r="F42">
-        <v>28.632</v>
+        <v>29.3478</v>
       </c>
       <c r="G42">
         <v>10.5</v>
@@ -4719,28 +4719,28 @@
         <v>7.819999999999999</v>
       </c>
       <c r="M42">
-        <v>1.5833496</v>
+        <v>1.62293334</v>
       </c>
       <c r="N42">
-        <v>6.236650399999999</v>
+        <v>6.197066659999999</v>
       </c>
       <c r="O42">
-        <v>1.122597072</v>
+        <v>1.1154719988</v>
       </c>
       <c r="P42">
-        <v>5.114053328</v>
+        <v>5.0815946612</v>
       </c>
       <c r="Q42">
-        <v>11.894053328</v>
+        <v>11.8615946612</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1114302886088787</v>
+        <v>0.1124132086238422</v>
       </c>
       <c r="T42">
-        <v>1.106620951836509</v>
+        <v>1.123194395372926</v>
       </c>
       <c r="U42">
         <v>0.0553</v>
@@ -4757,7 +4757,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>4.938896627756749</v>
+        <v>4.818435734396829</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4765,22 +4765,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.08491565308806691</v>
+        <v>0.08483473301080659</v>
       </c>
       <c r="C43">
-        <v>47.49993442904272</v>
+        <v>46.92167511094156</v>
       </c>
       <c r="D43">
-        <v>66.34773442904273</v>
+        <v>66.48527511094156</v>
       </c>
       <c r="E43">
-        <v>28.2678</v>
+        <v>28.9836</v>
       </c>
       <c r="F43">
-        <v>29.3478</v>
+        <v>30.0636</v>
       </c>
       <c r="G43">
         <v>10.5</v>
@@ -4801,28 +4801,28 @@
         <v>7.819999999999999</v>
       </c>
       <c r="M43">
-        <v>1.62293334</v>
+        <v>1.66251708</v>
       </c>
       <c r="N43">
-        <v>6.197066659999999</v>
+        <v>6.15748292</v>
       </c>
       <c r="O43">
-        <v>1.1154719988</v>
+        <v>1.1083469256</v>
       </c>
       <c r="P43">
-        <v>5.0815946612</v>
+        <v>5.0491359944</v>
       </c>
       <c r="Q43">
-        <v>11.8615946612</v>
+        <v>11.8291359944</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1124132086238422</v>
+        <v>0.1134300224324251</v>
       </c>
       <c r="T43">
-        <v>1.123194395372926</v>
+        <v>1.140339336962324</v>
       </c>
       <c r="U43">
         <v>0.0553</v>
@@ -4839,7 +4839,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>4.818435734396829</v>
+        <v>4.703711074054048</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4847,22 +4847,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.0848347330108066</v>
+        <v>0.08475381293354625</v>
       </c>
       <c r="C44">
-        <v>46.92167511094154</v>
+        <v>46.34398722869062</v>
       </c>
       <c r="D44">
-        <v>66.48527511094153</v>
+        <v>66.62338722869062</v>
       </c>
       <c r="E44">
-        <v>28.9836</v>
+        <v>29.6994</v>
       </c>
       <c r="F44">
-        <v>30.0636</v>
+        <v>30.7794</v>
       </c>
       <c r="G44">
         <v>10.5</v>
@@ -4883,28 +4883,28 @@
         <v>7.819999999999999</v>
       </c>
       <c r="M44">
-        <v>1.66251708</v>
+        <v>1.70210082</v>
       </c>
       <c r="N44">
-        <v>6.15748292</v>
+        <v>6.117899179999999</v>
       </c>
       <c r="O44">
-        <v>1.1083469256</v>
+        <v>1.1012218524</v>
       </c>
       <c r="P44">
-        <v>5.0491359944</v>
+        <v>5.016677327599999</v>
       </c>
       <c r="Q44">
-        <v>11.8291359944</v>
+        <v>11.7966773276</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1134300224324251</v>
+        <v>0.1144825139185022</v>
       </c>
       <c r="T44">
-        <v>1.140339336962324</v>
+        <v>1.158085855449595</v>
       </c>
       <c r="U44">
         <v>0.0553</v>
@@ -4921,7 +4921,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>4.703711074054048</v>
+        <v>4.594322444424884</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4929,22 +4929,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.08475381293354625</v>
+        <v>0.08557489285628592</v>
       </c>
       <c r="C45">
-        <v>46.34398722869062</v>
+        <v>44.25286924012832</v>
       </c>
       <c r="D45">
-        <v>66.62338722869062</v>
+        <v>65.24806924012832</v>
       </c>
       <c r="E45">
-        <v>29.6994</v>
+        <v>30.4152</v>
       </c>
       <c r="F45">
-        <v>30.7794</v>
+        <v>31.4952</v>
       </c>
       <c r="G45">
         <v>10.5</v>
@@ -4965,45 +4965,45 @@
         <v>7.819999999999999</v>
       </c>
       <c r="M45">
-        <v>1.70210082</v>
+        <v>1.82042256</v>
       </c>
       <c r="N45">
-        <v>6.117899179999999</v>
+        <v>5.999577439999999</v>
       </c>
       <c r="O45">
-        <v>1.1012218524</v>
+        <v>1.0799239392</v>
       </c>
       <c r="P45">
-        <v>5.016677327599999</v>
+        <v>4.919653500799999</v>
       </c>
       <c r="Q45">
-        <v>11.7966773276</v>
+        <v>11.6996535008</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1144825139185022</v>
+        <v>0.1155725943862248</v>
       </c>
       <c r="T45">
-        <v>1.158085855449595</v>
+        <v>1.176466178168554</v>
       </c>
       <c r="U45">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V45">
         <v>0.18</v>
       </c>
       <c r="W45">
-        <v>0.045346</v>
+        <v>0.04739600000000001</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y45">
-        <v>4.594322444424884</v>
+        <v>4.295705937636809</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5011,22 +5011,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.08557489285628592</v>
+        <v>0.08551447277902559</v>
       </c>
       <c r="C46">
-        <v>44.25286924012832</v>
+        <v>43.63633515274688</v>
       </c>
       <c r="D46">
-        <v>65.24806924012832</v>
+        <v>65.34733515274688</v>
       </c>
       <c r="E46">
-        <v>30.4152</v>
+        <v>31.131</v>
       </c>
       <c r="F46">
-        <v>31.4952</v>
+        <v>32.211</v>
       </c>
       <c r="G46">
         <v>10.5</v>
@@ -5047,28 +5047,28 @@
         <v>7.819999999999999</v>
       </c>
       <c r="M46">
-        <v>1.82042256</v>
+        <v>1.8617958</v>
       </c>
       <c r="N46">
-        <v>5.999577439999999</v>
+        <v>5.958204199999999</v>
       </c>
       <c r="O46">
-        <v>1.0799239392</v>
+        <v>1.072476756</v>
       </c>
       <c r="P46">
-        <v>4.919653500799999</v>
+        <v>4.885727444</v>
       </c>
       <c r="Q46">
-        <v>11.6996535008</v>
+        <v>11.665727444</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1155725943862248</v>
+        <v>0.1167023141436829</v>
       </c>
       <c r="T46">
-        <v>1.176466178168554</v>
+        <v>1.195514876259112</v>
       </c>
       <c r="U46">
         <v>0.0578</v>
@@ -5085,7 +5085,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>4.295705937636809</v>
+        <v>4.200245805689324</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5093,22 +5093,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.08551447277902559</v>
+        <v>0.08545405270176525</v>
       </c>
       <c r="C47">
-        <v>43.63633515274688</v>
+        <v>43.02010356428811</v>
       </c>
       <c r="D47">
-        <v>65.34733515274688</v>
+        <v>65.44690356428811</v>
       </c>
       <c r="E47">
-        <v>31.131</v>
+        <v>31.8468</v>
       </c>
       <c r="F47">
-        <v>32.211</v>
+        <v>32.9268</v>
       </c>
       <c r="G47">
         <v>10.5</v>
@@ -5129,28 +5129,28 @@
         <v>7.819999999999999</v>
       </c>
       <c r="M47">
-        <v>1.8617958</v>
+        <v>1.90316904</v>
       </c>
       <c r="N47">
-        <v>5.958204199999999</v>
+        <v>5.91683096</v>
       </c>
       <c r="O47">
-        <v>1.072476756</v>
+        <v>1.0650295728</v>
       </c>
       <c r="P47">
-        <v>4.885727444</v>
+        <v>4.8518013872</v>
       </c>
       <c r="Q47">
-        <v>11.665727444</v>
+        <v>11.6318013872</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1167023141436829</v>
+        <v>0.1178738753736393</v>
       </c>
       <c r="T47">
-        <v>1.195514876259112</v>
+        <v>1.215269081686357</v>
       </c>
       <c r="U47">
         <v>0.0578</v>
@@ -5167,7 +5167,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>4.200245805689324</v>
+        <v>4.108936114261295</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5175,22 +5175,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.08545405270176525</v>
+        <v>0.08539363262450492</v>
       </c>
       <c r="C48">
-        <v>43.02010356428811</v>
+        <v>42.40417585959642</v>
       </c>
       <c r="D48">
-        <v>65.44690356428811</v>
+        <v>65.54677585959642</v>
       </c>
       <c r="E48">
-        <v>31.8468</v>
+        <v>32.5626</v>
       </c>
       <c r="F48">
-        <v>32.9268</v>
+        <v>33.6426</v>
       </c>
       <c r="G48">
         <v>10.5</v>
@@ -5211,28 +5211,28 @@
         <v>7.819999999999999</v>
       </c>
       <c r="M48">
-        <v>1.90316904</v>
+        <v>1.94454228</v>
       </c>
       <c r="N48">
-        <v>5.91683096</v>
+        <v>5.875457719999999</v>
       </c>
       <c r="O48">
-        <v>1.0650295728</v>
+        <v>1.0575823896</v>
       </c>
       <c r="P48">
-        <v>4.8518013872</v>
+        <v>4.8178753304</v>
       </c>
       <c r="Q48">
-        <v>11.6318013872</v>
+        <v>11.5978753304</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1178738753736393</v>
+        <v>0.11908964646133</v>
       </c>
       <c r="T48">
-        <v>1.215269081686357</v>
+        <v>1.235768728827838</v>
       </c>
       <c r="U48">
         <v>0.0578</v>
@@ -5249,7 +5249,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>4.108936114261295</v>
+        <v>4.021511941617437</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5257,22 +5257,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.08539363262450492</v>
+        <v>0.08671081254724458</v>
       </c>
       <c r="C49">
-        <v>42.40417585959642</v>
+        <v>39.57800718718558</v>
       </c>
       <c r="D49">
-        <v>65.54677585959642</v>
+        <v>63.43640718718559</v>
       </c>
       <c r="E49">
-        <v>32.5626</v>
+        <v>33.2784</v>
       </c>
       <c r="F49">
-        <v>33.6426</v>
+        <v>34.3584</v>
       </c>
       <c r="G49">
         <v>10.5</v>
@@ -5293,45 +5293,45 @@
         <v>7.819999999999999</v>
       </c>
       <c r="M49">
-        <v>1.94454228</v>
+        <v>2.10616992</v>
       </c>
       <c r="N49">
-        <v>5.875457719999999</v>
+        <v>5.713830079999999</v>
       </c>
       <c r="O49">
-        <v>1.0575823896</v>
+        <v>1.0284894144</v>
       </c>
       <c r="P49">
-        <v>4.8178753304</v>
+        <v>4.685340665599999</v>
       </c>
       <c r="Q49">
-        <v>11.5978753304</v>
+        <v>11.4653406656</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.11908964646133</v>
+        <v>0.1203521779754703</v>
       </c>
       <c r="T49">
-        <v>1.235768728827838</v>
+        <v>1.257056823936299</v>
       </c>
       <c r="U49">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V49">
         <v>0.18</v>
       </c>
       <c r="W49">
-        <v>0.04739600000000001</v>
+        <v>0.05026600000000001</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y49">
-        <v>4.021511941617437</v>
+        <v>3.712900809066725</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5339,22 +5339,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.08671081254724458</v>
+        <v>0.08667909246998426</v>
       </c>
       <c r="C50">
-        <v>39.57800718718558</v>
+        <v>38.91143058270426</v>
       </c>
       <c r="D50">
-        <v>63.43640718718559</v>
+        <v>63.48563058270427</v>
       </c>
       <c r="E50">
-        <v>33.2784</v>
+        <v>33.9942</v>
       </c>
       <c r="F50">
-        <v>34.3584</v>
+        <v>35.0742</v>
       </c>
       <c r="G50">
         <v>10.5</v>
@@ -5375,28 +5375,28 @@
         <v>7.819999999999999</v>
       </c>
       <c r="M50">
-        <v>2.10616992</v>
+        <v>2.15004846</v>
       </c>
       <c r="N50">
-        <v>5.713830079999999</v>
+        <v>5.66995154</v>
       </c>
       <c r="O50">
-        <v>1.0284894144</v>
+        <v>1.0205912772</v>
       </c>
       <c r="P50">
-        <v>4.685340665599999</v>
+        <v>4.6493602628</v>
       </c>
       <c r="Q50">
-        <v>11.4653406656</v>
+        <v>11.4293602628</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1203521779754703</v>
+        <v>0.1216642205293809</v>
       </c>
       <c r="T50">
-        <v>1.257056823936299</v>
+        <v>1.279179746303915</v>
       </c>
       <c r="U50">
         <v>0.0613</v>
@@ -5413,7 +5413,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>3.712900809066725</v>
+        <v>3.637127323167404</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5421,22 +5421,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.08667909246998426</v>
+        <v>0.08664737239272392</v>
       </c>
       <c r="C51">
-        <v>38.91143058270426</v>
+        <v>38.2449304271996</v>
       </c>
       <c r="D51">
-        <v>63.48563058270427</v>
+        <v>63.5349304271996</v>
       </c>
       <c r="E51">
-        <v>33.9942</v>
+        <v>34.71</v>
       </c>
       <c r="F51">
-        <v>35.0742</v>
+        <v>35.79</v>
       </c>
       <c r="G51">
         <v>10.5</v>
@@ -5457,28 +5457,28 @@
         <v>7.819999999999999</v>
       </c>
       <c r="M51">
-        <v>2.15004846</v>
+        <v>2.193927</v>
       </c>
       <c r="N51">
-        <v>5.66995154</v>
+        <v>5.626073</v>
       </c>
       <c r="O51">
-        <v>1.0205912772</v>
+        <v>1.01269314</v>
       </c>
       <c r="P51">
-        <v>4.6493602628</v>
+        <v>4.61337986</v>
       </c>
       <c r="Q51">
-        <v>11.4293602628</v>
+        <v>11.39337986</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1216642205293809</v>
+        <v>0.1230287447854478</v>
       </c>
       <c r="T51">
-        <v>1.279179746303915</v>
+        <v>1.302187585566236</v>
       </c>
       <c r="U51">
         <v>0.0613</v>
@@ -5495,7 +5495,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>3.637127323167404</v>
+        <v>3.564384776704056</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5503,22 +5503,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.08664737239272392</v>
+        <v>0.08778661231546359</v>
       </c>
       <c r="C52">
-        <v>38.2449304271996</v>
+        <v>35.80521117676523</v>
       </c>
       <c r="D52">
-        <v>63.5349304271996</v>
+        <v>61.81101117676523</v>
       </c>
       <c r="E52">
-        <v>34.71</v>
+        <v>35.4258</v>
       </c>
       <c r="F52">
-        <v>35.79</v>
+        <v>36.5058</v>
       </c>
       <c r="G52">
         <v>10.5</v>
@@ -5539,45 +5539,45 @@
         <v>7.819999999999999</v>
       </c>
       <c r="M52">
-        <v>2.193927</v>
+        <v>2.34002178</v>
       </c>
       <c r="N52">
-        <v>5.626073</v>
+        <v>5.47997822</v>
       </c>
       <c r="O52">
-        <v>1.01269314</v>
+        <v>0.9863960795999999</v>
       </c>
       <c r="P52">
-        <v>4.61337986</v>
+        <v>4.4935821404</v>
       </c>
       <c r="Q52">
-        <v>11.39337986</v>
+        <v>11.2735821404</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1230287447854478</v>
+        <v>0.1244489639091094</v>
       </c>
       <c r="T52">
-        <v>1.302187585566236</v>
+        <v>1.326134520308652</v>
       </c>
       <c r="U52">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V52">
         <v>0.18</v>
       </c>
       <c r="W52">
-        <v>0.05026600000000001</v>
+        <v>0.052562</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y52">
-        <v>3.564384776704056</v>
+        <v>3.341849236975905</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5585,22 +5585,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.08778661231546359</v>
+        <v>0.08777785223820325</v>
       </c>
       <c r="C53">
-        <v>35.80521117676523</v>
+        <v>35.10231010333191</v>
       </c>
       <c r="D53">
-        <v>61.81101117676523</v>
+        <v>61.82391010333192</v>
       </c>
       <c r="E53">
-        <v>35.4258</v>
+        <v>36.1416</v>
       </c>
       <c r="F53">
-        <v>36.5058</v>
+        <v>37.2216</v>
       </c>
       <c r="G53">
         <v>10.5</v>
@@ -5621,28 +5621,28 @@
         <v>7.819999999999999</v>
       </c>
       <c r="M53">
-        <v>2.34002178</v>
+        <v>2.38590456</v>
       </c>
       <c r="N53">
-        <v>5.47997822</v>
+        <v>5.434095439999999</v>
       </c>
       <c r="O53">
-        <v>0.9863960795999999</v>
+        <v>0.9781371791999999</v>
       </c>
       <c r="P53">
-        <v>4.4935821404</v>
+        <v>4.455958260799999</v>
       </c>
       <c r="Q53">
-        <v>11.2735821404</v>
+        <v>11.2359582608</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1244489639091094</v>
+        <v>0.1259283588295901</v>
       </c>
       <c r="T53">
-        <v>1.326134520308652</v>
+        <v>1.351079243998669</v>
       </c>
       <c r="U53">
         <v>0.0641</v>
@@ -5659,7 +5659,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>3.341849236975905</v>
+        <v>3.277582905495599</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5667,22 +5667,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.08777785223820325</v>
+        <v>0.08776909216094292</v>
       </c>
       <c r="C54">
-        <v>35.10231010333191</v>
+        <v>34.39941441460376</v>
       </c>
       <c r="D54">
-        <v>61.82391010333192</v>
+        <v>61.83681441460376</v>
       </c>
       <c r="E54">
-        <v>36.1416</v>
+        <v>36.85740000000001</v>
       </c>
       <c r="F54">
-        <v>37.2216</v>
+        <v>37.9374</v>
       </c>
       <c r="G54">
         <v>10.5</v>
@@ -5703,28 +5703,28 @@
         <v>7.819999999999999</v>
       </c>
       <c r="M54">
-        <v>2.38590456</v>
+        <v>2.431787340000001</v>
       </c>
       <c r="N54">
-        <v>5.434095439999999</v>
+        <v>5.388212659999999</v>
       </c>
       <c r="O54">
-        <v>0.9781371791999999</v>
+        <v>0.9698782787999998</v>
       </c>
       <c r="P54">
-        <v>4.455958260799999</v>
+        <v>4.418334381199999</v>
       </c>
       <c r="Q54">
-        <v>11.2359582608</v>
+        <v>11.1983343812</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1259283588295901</v>
+        <v>0.1274707067254105</v>
       </c>
       <c r="T54">
-        <v>1.351079243998669</v>
+        <v>1.377085445292515</v>
       </c>
       <c r="U54">
         <v>0.0641</v>
@@ -5741,7 +5741,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>3.277582905495599</v>
+        <v>3.215741718599455</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5749,22 +5749,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.08776909216094292</v>
+        <v>0.08776033208368259</v>
       </c>
       <c r="C55">
-        <v>34.39941441460376</v>
+        <v>33.69652411395325</v>
       </c>
       <c r="D55">
-        <v>61.83681441460376</v>
+        <v>61.84972411395324</v>
       </c>
       <c r="E55">
-        <v>36.85740000000001</v>
+        <v>37.5732</v>
       </c>
       <c r="F55">
-        <v>37.9374</v>
+        <v>38.6532</v>
       </c>
       <c r="G55">
         <v>10.5</v>
@@ -5785,28 +5785,28 @@
         <v>7.819999999999999</v>
       </c>
       <c r="M55">
-        <v>2.431787340000001</v>
+        <v>2.47767012</v>
       </c>
       <c r="N55">
-        <v>5.388212659999999</v>
+        <v>5.342329879999999</v>
       </c>
       <c r="O55">
-        <v>0.9698782787999998</v>
+        <v>0.9616193783999999</v>
       </c>
       <c r="P55">
-        <v>4.418334381199999</v>
+        <v>4.380710501599999</v>
       </c>
       <c r="Q55">
-        <v>11.1983343812</v>
+        <v>11.1607105016</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1274707067254105</v>
+        <v>0.1290801132253969</v>
       </c>
       <c r="T55">
-        <v>1.377085445292515</v>
+        <v>1.404222350990442</v>
       </c>
       <c r="U55">
         <v>0.0641</v>
@@ -5823,7 +5823,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>3.215741718599455</v>
+        <v>3.156190946032799</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5831,22 +5831,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.08776033208368259</v>
+        <v>0.08775157200642225</v>
       </c>
       <c r="C56">
-        <v>33.69652411395325</v>
+        <v>32.99363920475568</v>
       </c>
       <c r="D56">
-        <v>61.84972411395324</v>
+        <v>61.86263920475569</v>
       </c>
       <c r="E56">
-        <v>37.5732</v>
+        <v>38.289</v>
       </c>
       <c r="F56">
-        <v>38.6532</v>
+        <v>39.369</v>
       </c>
       <c r="G56">
         <v>10.5</v>
@@ -5867,28 +5867,28 @@
         <v>7.819999999999999</v>
       </c>
       <c r="M56">
-        <v>2.47767012</v>
+        <v>2.5235529</v>
       </c>
       <c r="N56">
-        <v>5.342329879999999</v>
+        <v>5.296447099999999</v>
       </c>
       <c r="O56">
-        <v>0.9616193783999999</v>
+        <v>0.9533604779999998</v>
       </c>
       <c r="P56">
-        <v>4.380710501599999</v>
+        <v>4.343086622</v>
       </c>
       <c r="Q56">
-        <v>11.1607105016</v>
+        <v>11.123086622</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1290801132253969</v>
+        <v>0.1307610489031606</v>
       </c>
       <c r="T56">
-        <v>1.404222350990442</v>
+        <v>1.432565341386055</v>
       </c>
       <c r="U56">
         <v>0.0641</v>
@@ -5905,7 +5905,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>3.156190946032799</v>
+        <v>3.09880565610493</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5913,22 +5913,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.08775157200642225</v>
+        <v>0.08774281192916192</v>
       </c>
       <c r="C57">
-        <v>32.99363920475568</v>
+        <v>32.29075969038925</v>
       </c>
       <c r="D57">
-        <v>61.86263920475569</v>
+        <v>61.87555969038925</v>
       </c>
       <c r="E57">
-        <v>38.289</v>
+        <v>39.0048</v>
       </c>
       <c r="F57">
-        <v>39.369</v>
+        <v>40.0848</v>
       </c>
       <c r="G57">
         <v>10.5</v>
@@ -5949,28 +5949,28 @@
         <v>7.819999999999999</v>
       </c>
       <c r="M57">
-        <v>2.5235529</v>
+        <v>2.56943568</v>
       </c>
       <c r="N57">
-        <v>5.296447099999999</v>
+        <v>5.250564319999999</v>
       </c>
       <c r="O57">
-        <v>0.9533604779999998</v>
+        <v>0.9451015775999997</v>
       </c>
       <c r="P57">
-        <v>4.343086622</v>
+        <v>4.305462742399999</v>
       </c>
       <c r="Q57">
-        <v>11.123086622</v>
+        <v>11.0854627424</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1307610489031606</v>
+        <v>0.1325183907480953</v>
       </c>
       <c r="T57">
-        <v>1.432565341386055</v>
+        <v>1.462196649526923</v>
       </c>
       <c r="U57">
         <v>0.0641</v>
@@ -5987,7 +5987,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>3.09880565610493</v>
+        <v>3.043469840817342</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -5995,22 +5995,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.08774281192916192</v>
+        <v>0.09137977185190159</v>
       </c>
       <c r="C58">
-        <v>32.29075969038925</v>
+        <v>26.63770525387667</v>
       </c>
       <c r="D58">
-        <v>61.87555969038925</v>
+        <v>56.93830525387667</v>
       </c>
       <c r="E58">
-        <v>39.0048</v>
+        <v>39.7206</v>
       </c>
       <c r="F58">
-        <v>40.0848</v>
+        <v>40.8006</v>
       </c>
       <c r="G58">
         <v>10.5</v>
@@ -6031,45 +6031,45 @@
         <v>7.819999999999999</v>
       </c>
       <c r="M58">
-        <v>2.56943568</v>
+        <v>2.93356314</v>
       </c>
       <c r="N58">
-        <v>5.250564319999999</v>
+        <v>4.886436859999999</v>
       </c>
       <c r="O58">
-        <v>0.9451015775999997</v>
+        <v>0.8795586347999997</v>
       </c>
       <c r="P58">
-        <v>4.305462742399999</v>
+        <v>4.006878225199999</v>
       </c>
       <c r="Q58">
-        <v>11.0854627424</v>
+        <v>10.7868782252</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1325183907480953</v>
+        <v>0.134357469423027</v>
       </c>
       <c r="T58">
-        <v>1.462196649526923</v>
+        <v>1.493206158046436</v>
       </c>
       <c r="U58">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V58">
         <v>0.18</v>
       </c>
       <c r="W58">
-        <v>0.052562</v>
+        <v>0.05895800000000001</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y58">
-        <v>3.043469840817342</v>
+        <v>2.665700251469617</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6077,22 +6077,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.09137977185190159</v>
+        <v>0.09143497177464126</v>
       </c>
       <c r="C59">
-        <v>26.63770525387667</v>
+        <v>25.85303285341891</v>
       </c>
       <c r="D59">
-        <v>56.93830525387667</v>
+        <v>56.86943285341891</v>
       </c>
       <c r="E59">
-        <v>39.7206</v>
+        <v>40.43640000000001</v>
       </c>
       <c r="F59">
-        <v>40.8006</v>
+        <v>41.5164</v>
       </c>
       <c r="G59">
         <v>10.5</v>
@@ -6113,28 +6113,28 @@
         <v>7.819999999999999</v>
       </c>
       <c r="M59">
-        <v>2.93356314</v>
+        <v>2.985029160000001</v>
       </c>
       <c r="N59">
-        <v>4.886436859999999</v>
+        <v>4.834970839999999</v>
       </c>
       <c r="O59">
-        <v>0.8795586347999997</v>
+        <v>0.8702947511999998</v>
       </c>
       <c r="P59">
-        <v>4.006878225199999</v>
+        <v>3.964676088799999</v>
       </c>
       <c r="Q59">
-        <v>10.7868782252</v>
+        <v>10.7446760888</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.134357469423027</v>
+        <v>0.1362841232729554</v>
       </c>
       <c r="T59">
-        <v>1.493206158046436</v>
+        <v>1.525692309828782</v>
       </c>
       <c r="U59">
         <v>0.07190000000000001</v>
@@ -6151,7 +6151,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>2.665700251469617</v>
+        <v>2.619739902306347</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6159,22 +6159,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.09143497177464127</v>
+        <v>0.09149017169738093</v>
       </c>
       <c r="C60">
-        <v>25.85303285341889</v>
+        <v>25.06852686735808</v>
       </c>
       <c r="D60">
-        <v>56.86943285341889</v>
+        <v>56.80072686735808</v>
       </c>
       <c r="E60">
-        <v>40.4364</v>
+        <v>41.1522</v>
       </c>
       <c r="F60">
-        <v>41.5164</v>
+        <v>42.2322</v>
       </c>
       <c r="G60">
         <v>10.5</v>
@@ -6195,28 +6195,28 @@
         <v>7.819999999999999</v>
       </c>
       <c r="M60">
-        <v>2.98502916</v>
+        <v>3.03649518</v>
       </c>
       <c r="N60">
-        <v>4.83497084</v>
+        <v>4.783504819999999</v>
       </c>
       <c r="O60">
-        <v>0.8702947511999999</v>
+        <v>0.8610308675999998</v>
       </c>
       <c r="P60">
-        <v>3.9646760888</v>
+        <v>3.922473952399999</v>
       </c>
       <c r="Q60">
-        <v>10.7446760888</v>
+        <v>10.7024739524</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1362841232729554</v>
+        <v>0.1383047602375144</v>
       </c>
       <c r="T60">
-        <v>1.525692309828782</v>
+        <v>1.559763151941975</v>
       </c>
       <c r="U60">
         <v>0.07190000000000001</v>
@@ -6233,7 +6233,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>2.619739902306348</v>
+        <v>2.575337531080816</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6241,22 +6241,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.09149017169738093</v>
+        <v>0.09154537162012058</v>
       </c>
       <c r="C61">
-        <v>25.06852686735808</v>
+        <v>24.28418669326852</v>
       </c>
       <c r="D61">
-        <v>56.80072686735808</v>
+        <v>56.73218669326852</v>
       </c>
       <c r="E61">
-        <v>41.1522</v>
+        <v>41.868</v>
       </c>
       <c r="F61">
-        <v>42.2322</v>
+        <v>42.948</v>
       </c>
       <c r="G61">
         <v>10.5</v>
@@ -6277,28 +6277,28 @@
         <v>7.819999999999999</v>
       </c>
       <c r="M61">
-        <v>3.03649518</v>
+        <v>3.0879612</v>
       </c>
       <c r="N61">
-        <v>4.783504819999999</v>
+        <v>4.7320388</v>
       </c>
       <c r="O61">
-        <v>0.8610308675999998</v>
+        <v>0.8517669839999999</v>
       </c>
       <c r="P61">
-        <v>3.922473952399999</v>
+        <v>3.880271816</v>
       </c>
       <c r="Q61">
-        <v>10.7024739524</v>
+        <v>10.660271816</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1383047602375144</v>
+        <v>0.1404264290503014</v>
       </c>
       <c r="T61">
-        <v>1.559763151941975</v>
+        <v>1.595537536160828</v>
       </c>
       <c r="U61">
         <v>0.07190000000000001</v>
@@ -6315,7 +6315,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>2.575337531080816</v>
+        <v>2.532415238896136</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6323,22 +6323,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.09154537162012058</v>
+        <v>0.09355135154286026</v>
       </c>
       <c r="C62">
-        <v>24.28418669326852</v>
+        <v>21.1851321087848</v>
       </c>
       <c r="D62">
-        <v>56.73218669326852</v>
+        <v>54.34893210878479</v>
       </c>
       <c r="E62">
-        <v>41.868</v>
+        <v>42.5838</v>
       </c>
       <c r="F62">
-        <v>42.948</v>
+        <v>43.66379999999999</v>
       </c>
       <c r="G62">
         <v>10.5</v>
@@ -6359,45 +6359,45 @@
         <v>7.819999999999999</v>
       </c>
       <c r="M62">
-        <v>3.0879612</v>
+        <v>3.30971604</v>
       </c>
       <c r="N62">
-        <v>4.7320388</v>
+        <v>4.510283959999999</v>
       </c>
       <c r="O62">
-        <v>0.8517669839999999</v>
+        <v>0.8118511127999998</v>
       </c>
       <c r="P62">
-        <v>3.880271816</v>
+        <v>3.698432847199999</v>
       </c>
       <c r="Q62">
-        <v>10.660271816</v>
+        <v>10.4784328472</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1404264290503014</v>
+        <v>0.1426569013919494</v>
       </c>
       <c r="T62">
-        <v>1.595537536160828</v>
+        <v>1.633146504185776</v>
       </c>
       <c r="U62">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V62">
         <v>0.18</v>
       </c>
       <c r="W62">
-        <v>0.05895800000000001</v>
+        <v>0.06215600000000001</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y62">
-        <v>2.532415238896136</v>
+        <v>2.362740460356834</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6405,22 +6405,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.09355135154286026</v>
+        <v>0.09363853146559992</v>
       </c>
       <c r="C63">
-        <v>21.1851321087848</v>
+        <v>20.37028777031814</v>
       </c>
       <c r="D63">
-        <v>54.34893210878479</v>
+        <v>54.24988777031813</v>
       </c>
       <c r="E63">
-        <v>42.5838</v>
+        <v>43.2996</v>
       </c>
       <c r="F63">
-        <v>43.66379999999999</v>
+        <v>44.3796</v>
       </c>
       <c r="G63">
         <v>10.5</v>
@@ -6441,28 +6441,28 @@
         <v>7.819999999999999</v>
       </c>
       <c r="M63">
-        <v>3.30971604</v>
+        <v>3.36397368</v>
       </c>
       <c r="N63">
-        <v>4.510283959999999</v>
+        <v>4.456026319999999</v>
       </c>
       <c r="O63">
-        <v>0.8118511127999998</v>
+        <v>0.8020847375999999</v>
       </c>
       <c r="P63">
-        <v>3.698432847199999</v>
+        <v>3.653941582399999</v>
       </c>
       <c r="Q63">
-        <v>10.4784328472</v>
+        <v>10.4339415824</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1426569013919494</v>
+        <v>0.1450047670147366</v>
       </c>
       <c r="T63">
-        <v>1.633146504185776</v>
+        <v>1.672734891580457</v>
       </c>
       <c r="U63">
         <v>0.07580000000000001</v>
@@ -6479,7 +6479,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>2.362740460356834</v>
+        <v>2.324631743254305</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6487,22 +6487,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.09363853146559992</v>
+        <v>0.09372571138833959</v>
       </c>
       <c r="C64">
-        <v>20.37028777031814</v>
+        <v>19.5558037677766</v>
       </c>
       <c r="D64">
-        <v>54.24988777031813</v>
+        <v>54.1512037677766</v>
       </c>
       <c r="E64">
-        <v>43.2996</v>
+        <v>44.0154</v>
       </c>
       <c r="F64">
-        <v>44.3796</v>
+        <v>45.0954</v>
       </c>
       <c r="G64">
         <v>10.5</v>
@@ -6523,28 +6523,28 @@
         <v>7.819999999999999</v>
       </c>
       <c r="M64">
-        <v>3.36397368</v>
+        <v>3.41823132</v>
       </c>
       <c r="N64">
-        <v>4.456026319999999</v>
+        <v>4.401768679999999</v>
       </c>
       <c r="O64">
-        <v>0.8020847375999999</v>
+        <v>0.7923183623999998</v>
       </c>
       <c r="P64">
-        <v>3.653941582399999</v>
+        <v>3.609450317599999</v>
       </c>
       <c r="Q64">
-        <v>10.4339415824</v>
+        <v>10.3894503176</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1450047670147366</v>
+        <v>0.1474795442928097</v>
       </c>
       <c r="T64">
-        <v>1.672734891580457</v>
+        <v>1.714463191807284</v>
       </c>
       <c r="U64">
         <v>0.07580000000000001</v>
@@ -6561,7 +6561,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>2.324631743254305</v>
+        <v>2.287732826694713</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6569,22 +6569,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.09372571138833959</v>
+        <v>0.09381289131107926</v>
       </c>
       <c r="C65">
-        <v>19.5558037677766</v>
+        <v>18.74167813830873</v>
       </c>
       <c r="D65">
-        <v>54.1512037677766</v>
+        <v>54.05287813830872</v>
       </c>
       <c r="E65">
-        <v>44.0154</v>
+        <v>44.7312</v>
       </c>
       <c r="F65">
-        <v>45.0954</v>
+        <v>45.8112</v>
       </c>
       <c r="G65">
         <v>10.5</v>
@@ -6605,28 +6605,28 @@
         <v>7.819999999999999</v>
       </c>
       <c r="M65">
-        <v>3.41823132</v>
+        <v>3.47248896</v>
       </c>
       <c r="N65">
-        <v>4.401768679999999</v>
+        <v>4.347511039999999</v>
       </c>
       <c r="O65">
-        <v>0.7923183623999998</v>
+        <v>0.7825519871999997</v>
       </c>
       <c r="P65">
-        <v>3.609450317599999</v>
+        <v>3.564959052799999</v>
       </c>
       <c r="Q65">
-        <v>10.3894503176</v>
+        <v>10.3449590528</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1474795442928097</v>
+        <v>0.1500918091974424</v>
       </c>
       <c r="T65">
-        <v>1.714463191807284</v>
+        <v>1.758509730935601</v>
       </c>
       <c r="U65">
         <v>0.07580000000000001</v>
@@ -6643,7 +6643,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>2.287732826694713</v>
+        <v>2.251987001277608</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6651,22 +6651,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.09381289131107926</v>
+        <v>0.09390007123381894</v>
       </c>
       <c r="C66">
-        <v>18.74167813830873</v>
+        <v>17.92790893329344</v>
       </c>
       <c r="D66">
-        <v>54.05287813830872</v>
+        <v>53.95490893329345</v>
       </c>
       <c r="E66">
-        <v>44.7312</v>
+        <v>45.447</v>
       </c>
       <c r="F66">
-        <v>45.8112</v>
+        <v>46.527</v>
       </c>
       <c r="G66">
         <v>10.5</v>
@@ -6687,28 +6687,28 @@
         <v>7.819999999999999</v>
       </c>
       <c r="M66">
-        <v>3.47248896</v>
+        <v>3.526746600000001</v>
       </c>
       <c r="N66">
-        <v>4.347511039999999</v>
+        <v>4.293253399999999</v>
       </c>
       <c r="O66">
-        <v>0.7825519871999997</v>
+        <v>0.7727856119999998</v>
       </c>
       <c r="P66">
-        <v>3.564959052799999</v>
+        <v>3.520467787999999</v>
       </c>
       <c r="Q66">
-        <v>10.3449590528</v>
+        <v>10.300467788</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1500918091974424</v>
+        <v>0.1528533463823398</v>
       </c>
       <c r="T66">
-        <v>1.758509730935601</v>
+        <v>1.805073215156965</v>
       </c>
       <c r="U66">
         <v>0.07580000000000001</v>
@@ -6725,7 +6725,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>2.251987001277608</v>
+        <v>2.217341047411798</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6733,22 +6733,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.09390007123381894</v>
+        <v>0.09398725115655859</v>
       </c>
       <c r="C67">
-        <v>17.92790893329344</v>
+        <v>17.11449421821149</v>
       </c>
       <c r="D67">
-        <v>53.95490893329345</v>
+        <v>53.85729421821149</v>
       </c>
       <c r="E67">
-        <v>45.447</v>
+        <v>46.1628</v>
       </c>
       <c r="F67">
-        <v>46.527</v>
+        <v>47.2428</v>
       </c>
       <c r="G67">
         <v>10.5</v>
@@ -6769,28 +6769,28 @@
         <v>7.819999999999999</v>
       </c>
       <c r="M67">
-        <v>3.526746600000001</v>
+        <v>3.58100424</v>
       </c>
       <c r="N67">
-        <v>4.293253399999999</v>
+        <v>4.238995759999999</v>
       </c>
       <c r="O67">
-        <v>0.7727856119999998</v>
+        <v>0.7630192367999998</v>
       </c>
       <c r="P67">
-        <v>3.520467787999999</v>
+        <v>3.475976523199999</v>
       </c>
       <c r="Q67">
-        <v>10.300467788</v>
+        <v>10.2559765232</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1528533463823398</v>
+        <v>0.1557773269310547</v>
       </c>
       <c r="T67">
-        <v>1.805073215156965</v>
+        <v>1.854375727861938</v>
       </c>
       <c r="U67">
         <v>0.07580000000000001</v>
@@ -6807,7 +6807,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>2.217341047411798</v>
+        <v>2.183744970935862</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6815,22 +6815,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.09398725115655859</v>
+        <v>0.09407443107929826</v>
       </c>
       <c r="C68">
-        <v>17.11449421821149</v>
+        <v>16.30143207251787</v>
       </c>
       <c r="D68">
-        <v>53.85729421821149</v>
+        <v>53.76003207251788</v>
       </c>
       <c r="E68">
-        <v>46.1628</v>
+        <v>46.87860000000001</v>
       </c>
       <c r="F68">
-        <v>47.2428</v>
+        <v>47.9586</v>
       </c>
       <c r="G68">
         <v>10.5</v>
@@ -6851,28 +6851,28 @@
         <v>7.819999999999999</v>
       </c>
       <c r="M68">
-        <v>3.58100424</v>
+        <v>3.635261880000001</v>
       </c>
       <c r="N68">
-        <v>4.238995759999999</v>
+        <v>4.184738119999999</v>
       </c>
       <c r="O68">
-        <v>0.7630192367999998</v>
+        <v>0.7532528615999997</v>
       </c>
       <c r="P68">
-        <v>3.475976523199999</v>
+        <v>3.431485258399999</v>
       </c>
       <c r="Q68">
-        <v>10.2559765232</v>
+        <v>10.2114852584</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1557773269310547</v>
+        <v>0.1588785184221159</v>
       </c>
       <c r="T68">
-        <v>1.854375727861938</v>
+        <v>1.906666271639941</v>
       </c>
       <c r="U68">
         <v>0.07580000000000001</v>
@@ -6889,7 +6889,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>2.183744970935862</v>
+        <v>2.151151762414431</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6897,22 +6897,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.09407443107929826</v>
+        <v>0.09416161100203793</v>
       </c>
       <c r="C69">
-        <v>16.30143207251787</v>
+        <v>15.48872058951606</v>
       </c>
       <c r="D69">
-        <v>53.76003207251788</v>
+        <v>53.66312058951606</v>
       </c>
       <c r="E69">
-        <v>46.87860000000001</v>
+        <v>47.59440000000001</v>
       </c>
       <c r="F69">
-        <v>47.9586</v>
+        <v>48.67440000000001</v>
       </c>
       <c r="G69">
         <v>10.5</v>
@@ -6933,28 +6933,28 @@
         <v>7.819999999999999</v>
       </c>
       <c r="M69">
-        <v>3.635261880000001</v>
+        <v>3.689519520000001</v>
       </c>
       <c r="N69">
-        <v>4.184738119999999</v>
+        <v>4.130480479999999</v>
       </c>
       <c r="O69">
-        <v>0.7532528615999997</v>
+        <v>0.7434864863999998</v>
       </c>
       <c r="P69">
-        <v>3.431485258399999</v>
+        <v>3.3869939936</v>
       </c>
       <c r="Q69">
-        <v>10.2114852584</v>
+        <v>10.1669939936</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1588785184221159</v>
+        <v>0.1621735343813685</v>
       </c>
       <c r="T69">
-        <v>1.906666271639941</v>
+        <v>1.962224974404068</v>
       </c>
       <c r="U69">
         <v>0.07580000000000001</v>
@@ -6971,7 +6971,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>2.151151762414431</v>
+        <v>2.119517177673043</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6979,22 +6979,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.09416161100203793</v>
+        <v>0.0942487909247776</v>
       </c>
       <c r="C70">
-        <v>15.48872058951606</v>
+        <v>14.67635787623335</v>
       </c>
       <c r="D70">
-        <v>53.66312058951606</v>
+        <v>53.56655787623335</v>
       </c>
       <c r="E70">
-        <v>47.59440000000001</v>
+        <v>48.3102</v>
       </c>
       <c r="F70">
-        <v>48.67440000000001</v>
+        <v>49.3902</v>
       </c>
       <c r="G70">
         <v>10.5</v>
@@ -7015,28 +7015,28 @@
         <v>7.819999999999999</v>
       </c>
       <c r="M70">
-        <v>3.689519520000001</v>
+        <v>3.74377716</v>
       </c>
       <c r="N70">
-        <v>4.130480479999999</v>
+        <v>4.076222839999999</v>
       </c>
       <c r="O70">
-        <v>0.7434864863999998</v>
+        <v>0.7337201111999998</v>
       </c>
       <c r="P70">
-        <v>3.3869939936</v>
+        <v>3.342502728799999</v>
       </c>
       <c r="Q70">
-        <v>10.1669939936</v>
+        <v>10.1225027288</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1621735343813685</v>
+        <v>0.1656811320154116</v>
       </c>
       <c r="T70">
-        <v>1.962224974404068</v>
+        <v>2.021368109604591</v>
       </c>
       <c r="U70">
         <v>0.07580000000000001</v>
@@ -7053,7 +7053,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>2.119517177673043</v>
+        <v>2.088799537416912</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7061,22 +7061,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.0942487909247776</v>
+        <v>0.09433597084751727</v>
       </c>
       <c r="C71">
-        <v>14.67635787623335</v>
+        <v>13.86434205329758</v>
       </c>
       <c r="D71">
-        <v>53.56655787623335</v>
+        <v>53.47034205329759</v>
       </c>
       <c r="E71">
-        <v>48.3102</v>
+        <v>49.026</v>
       </c>
       <c r="F71">
-        <v>49.3902</v>
+        <v>50.106</v>
       </c>
       <c r="G71">
         <v>10.5</v>
@@ -7097,28 +7097,28 @@
         <v>7.819999999999999</v>
       </c>
       <c r="M71">
-        <v>3.74377716</v>
+        <v>3.7980348</v>
       </c>
       <c r="N71">
-        <v>4.076222839999999</v>
+        <v>4.021965199999999</v>
       </c>
       <c r="O71">
-        <v>0.7337201111999998</v>
+        <v>0.7239537359999997</v>
       </c>
       <c r="P71">
-        <v>3.342502728799999</v>
+        <v>3.298011463999999</v>
       </c>
       <c r="Q71">
-        <v>10.1225027288</v>
+        <v>10.078011464</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1656811320154116</v>
+        <v>0.1694225694917242</v>
       </c>
       <c r="T71">
-        <v>2.021368109604591</v>
+        <v>2.084454120485148</v>
       </c>
       <c r="U71">
         <v>0.07580000000000001</v>
@@ -7135,7 +7135,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>2.088799537416912</v>
+        <v>2.058959544025242</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7143,22 +7143,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.09433597084751727</v>
+        <v>0.09442315077025693</v>
       </c>
       <c r="C72">
-        <v>13.86434205329758</v>
+        <v>13.05267125481529</v>
       </c>
       <c r="D72">
-        <v>53.47034205329759</v>
+        <v>53.3744712548153</v>
       </c>
       <c r="E72">
-        <v>49.026</v>
+        <v>49.7418</v>
       </c>
       <c r="F72">
-        <v>50.106</v>
+        <v>50.8218</v>
       </c>
       <c r="G72">
         <v>10.5</v>
@@ -7179,28 +7179,28 @@
         <v>7.819999999999999</v>
       </c>
       <c r="M72">
-        <v>3.7980348</v>
+        <v>3.852292440000001</v>
       </c>
       <c r="N72">
-        <v>4.021965199999999</v>
+        <v>3.967707559999999</v>
       </c>
       <c r="O72">
-        <v>0.7239537359999997</v>
+        <v>0.7141873607999998</v>
       </c>
       <c r="P72">
-        <v>3.298011463999999</v>
+        <v>3.253520199199999</v>
       </c>
       <c r="Q72">
-        <v>10.078011464</v>
+        <v>10.0335201992</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1694225694917242</v>
+        <v>0.173422037138817</v>
       </c>
       <c r="T72">
-        <v>2.084454120485148</v>
+        <v>2.151890890736778</v>
       </c>
       <c r="U72">
         <v>0.07580000000000001</v>
@@ -7217,7 +7217,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>2.058959544025242</v>
+        <v>2.029960113827703</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7225,22 +7225,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.09442315077025694</v>
+        <v>0.09451033069299661</v>
       </c>
       <c r="C73">
-        <v>13.05267125481528</v>
+        <v>12.24134362825095</v>
       </c>
       <c r="D73">
-        <v>53.37447125481528</v>
+        <v>53.27894362825095</v>
       </c>
       <c r="E73">
-        <v>49.7418</v>
+        <v>50.4576</v>
       </c>
       <c r="F73">
-        <v>50.8218</v>
+        <v>51.5376</v>
       </c>
       <c r="G73">
         <v>10.5</v>
@@ -7261,28 +7261,28 @@
         <v>7.819999999999999</v>
       </c>
       <c r="M73">
-        <v>3.85229244</v>
+        <v>3.90655008</v>
       </c>
       <c r="N73">
-        <v>3.96770756</v>
+        <v>3.913449919999999</v>
       </c>
       <c r="O73">
-        <v>0.7141873607999999</v>
+        <v>0.7044209855999999</v>
       </c>
       <c r="P73">
-        <v>3.2535201992</v>
+        <v>3.209028934399999</v>
       </c>
       <c r="Q73">
-        <v>10.0335201992</v>
+        <v>9.9890289344</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.173422037138817</v>
+        <v>0.1777071810464164</v>
       </c>
       <c r="T73">
-        <v>2.151890890736778</v>
+        <v>2.224144573149239</v>
       </c>
       <c r="U73">
         <v>0.07580000000000001</v>
@@ -7299,7 +7299,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>2.029960113827703</v>
+        <v>2.001766223357873</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7307,22 +7307,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.09451033069299661</v>
+        <v>0.1030976306157363</v>
       </c>
       <c r="C74">
-        <v>12.24134362825095</v>
+        <v>3.540531620147505</v>
       </c>
       <c r="D74">
-        <v>53.27894362825095</v>
+        <v>45.2939316201475</v>
       </c>
       <c r="E74">
-        <v>50.4576</v>
+        <v>51.1734</v>
       </c>
       <c r="F74">
-        <v>51.5376</v>
+        <v>52.2534</v>
       </c>
       <c r="G74">
         <v>10.5</v>
@@ -7343,45 +7343,45 @@
         <v>7.819999999999999</v>
       </c>
       <c r="M74">
-        <v>3.90655008</v>
+        <v>4.702806</v>
       </c>
       <c r="N74">
-        <v>3.913449919999999</v>
+        <v>3.117194</v>
       </c>
       <c r="O74">
-        <v>0.7044209855999999</v>
+        <v>0.5610949199999999</v>
       </c>
       <c r="P74">
-        <v>3.209028934399999</v>
+        <v>2.55609908</v>
       </c>
       <c r="Q74">
-        <v>9.9890289344</v>
+        <v>9.33609908</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1777071810464164</v>
+        <v>0.1823097430212454</v>
       </c>
       <c r="T74">
-        <v>2.224144573149239</v>
+        <v>2.301750380184845</v>
       </c>
       <c r="U74">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V74">
         <v>0.18</v>
       </c>
       <c r="W74">
-        <v>0.06215600000000001</v>
+        <v>0.0738</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y74">
-        <v>2.001766223357873</v>
+        <v>1.66283703814276</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7389,22 +7389,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.1030976306157363</v>
+        <v>0.1033012505384759</v>
       </c>
       <c r="C75">
-        <v>3.540531620147505</v>
+        <v>2.664339510920257</v>
       </c>
       <c r="D75">
-        <v>45.2939316201475</v>
+        <v>45.13353951092026</v>
       </c>
       <c r="E75">
-        <v>51.1734</v>
+        <v>51.8892</v>
       </c>
       <c r="F75">
-        <v>52.2534</v>
+        <v>52.9692</v>
       </c>
       <c r="G75">
         <v>10.5</v>
@@ -7425,28 +7425,28 @@
         <v>7.819999999999999</v>
       </c>
       <c r="M75">
-        <v>4.702806</v>
+        <v>4.767228</v>
       </c>
       <c r="N75">
-        <v>3.117194</v>
+        <v>3.052771999999999</v>
       </c>
       <c r="O75">
-        <v>0.5610949199999999</v>
+        <v>0.5494989599999999</v>
       </c>
       <c r="P75">
-        <v>2.55609908</v>
+        <v>2.503273039999999</v>
       </c>
       <c r="Q75">
-        <v>9.33609908</v>
+        <v>9.283273039999999</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1823097430212454</v>
+        <v>0.1872663482249074</v>
       </c>
       <c r="T75">
-        <v>2.301750380184845</v>
+        <v>2.385325864684729</v>
       </c>
       <c r="U75">
         <v>0.09</v>
@@ -7463,7 +7463,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>1.66283703814276</v>
+        <v>1.640366267357047</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7471,22 +7471,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.1033012505384759</v>
+        <v>0.1035048704612156</v>
       </c>
       <c r="C76">
-        <v>2.664339510920257</v>
+        <v>1.789279334877442</v>
       </c>
       <c r="D76">
-        <v>45.13353951092026</v>
+        <v>44.97427933487744</v>
       </c>
       <c r="E76">
-        <v>51.8892</v>
+        <v>52.605</v>
       </c>
       <c r="F76">
-        <v>52.9692</v>
+        <v>53.685</v>
       </c>
       <c r="G76">
         <v>10.5</v>
@@ -7507,28 +7507,28 @@
         <v>7.819999999999999</v>
       </c>
       <c r="M76">
-        <v>4.767228</v>
+        <v>4.83165</v>
       </c>
       <c r="N76">
-        <v>3.052771999999999</v>
+        <v>2.98835</v>
       </c>
       <c r="O76">
-        <v>0.5494989599999999</v>
+        <v>0.5379029999999999</v>
       </c>
       <c r="P76">
-        <v>2.503273039999999</v>
+        <v>2.450447</v>
       </c>
       <c r="Q76">
-        <v>9.283273039999999</v>
+        <v>9.230447</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.1872663482249074</v>
+        <v>0.1926194818448624</v>
       </c>
       <c r="T76">
-        <v>2.385325864684729</v>
+        <v>2.475587387944603</v>
       </c>
       <c r="U76">
         <v>0.09</v>
@@ -7545,7 +7545,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>1.640366267357047</v>
+        <v>1.618494717125619</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7553,22 +7553,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.1035048704612156</v>
+        <v>0.1037084903839553</v>
       </c>
       <c r="C77">
-        <v>1.789279334877442</v>
+        <v>0.9153391515861671</v>
       </c>
       <c r="D77">
-        <v>44.97427933487744</v>
+        <v>44.81613915158616</v>
       </c>
       <c r="E77">
-        <v>52.605</v>
+        <v>53.3208</v>
       </c>
       <c r="F77">
-        <v>53.685</v>
+        <v>54.4008</v>
       </c>
       <c r="G77">
         <v>10.5</v>
@@ -7589,28 +7589,28 @@
         <v>7.819999999999999</v>
       </c>
       <c r="M77">
-        <v>4.83165</v>
+        <v>4.896071999999999</v>
       </c>
       <c r="N77">
-        <v>2.98835</v>
+        <v>2.923928</v>
       </c>
       <c r="O77">
-        <v>0.5379029999999999</v>
+        <v>0.5263070399999999</v>
       </c>
       <c r="P77">
-        <v>2.450447</v>
+        <v>2.39762096</v>
       </c>
       <c r="Q77">
-        <v>9.230447</v>
+        <v>9.17762096</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.1926194818448624</v>
+        <v>0.1984187099331469</v>
       </c>
       <c r="T77">
-        <v>2.475587387944603</v>
+        <v>2.573370704809467</v>
       </c>
       <c r="U77">
         <v>0.09</v>
@@ -7627,7 +7627,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>1.618494717125619</v>
+        <v>1.597198734005546</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7635,22 +7635,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.1037084903839553</v>
+        <v>0.1039121103066949</v>
       </c>
       <c r="C78">
-        <v>0.9153391515861671</v>
+        <v>0.04250718796662767</v>
       </c>
       <c r="D78">
-        <v>44.81613915158616</v>
+        <v>44.65910718796663</v>
       </c>
       <c r="E78">
-        <v>53.3208</v>
+        <v>54.0366</v>
       </c>
       <c r="F78">
-        <v>54.4008</v>
+        <v>55.1166</v>
       </c>
       <c r="G78">
         <v>10.5</v>
@@ -7671,28 +7671,28 @@
         <v>7.819999999999999</v>
       </c>
       <c r="M78">
-        <v>4.896071999999999</v>
+        <v>4.960494</v>
       </c>
       <c r="N78">
-        <v>2.923928</v>
+        <v>2.859506</v>
       </c>
       <c r="O78">
-        <v>0.5263070399999999</v>
+        <v>0.5147110799999999</v>
       </c>
       <c r="P78">
-        <v>2.39762096</v>
+        <v>2.34479492</v>
       </c>
       <c r="Q78">
-        <v>9.17762096</v>
+        <v>9.124794919999999</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.1984187099331469</v>
+        <v>0.2047222187247606</v>
       </c>
       <c r="T78">
-        <v>2.573370704809467</v>
+        <v>2.679656918793015</v>
       </c>
       <c r="U78">
         <v>0.09</v>
@@ -7709,7 +7709,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>1.597198734005546</v>
+        <v>1.576455893304175</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7717,22 +7717,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.1039121103066949</v>
+        <v>0.1041157302294346</v>
       </c>
       <c r="C79">
-        <v>0.04250718796662767</v>
+        <v>-0.8292281646296615</v>
       </c>
       <c r="D79">
-        <v>44.65910718796663</v>
+        <v>44.50317183537034</v>
       </c>
       <c r="E79">
-        <v>54.0366</v>
+        <v>54.7524</v>
       </c>
       <c r="F79">
-        <v>55.1166</v>
+        <v>55.8324</v>
       </c>
       <c r="G79">
         <v>10.5</v>
@@ -7753,28 +7753,28 @@
         <v>7.819999999999999</v>
       </c>
       <c r="M79">
-        <v>4.960494</v>
+        <v>5.024916</v>
       </c>
       <c r="N79">
-        <v>2.859506</v>
+        <v>2.795083999999999</v>
       </c>
       <c r="O79">
-        <v>0.5147110799999999</v>
+        <v>0.5031151199999998</v>
       </c>
       <c r="P79">
-        <v>2.34479492</v>
+        <v>2.291968879999999</v>
       </c>
       <c r="Q79">
-        <v>9.124794919999999</v>
+        <v>9.07196888</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.2047222187247606</v>
+        <v>0.2115987737701573</v>
       </c>
       <c r="T79">
-        <v>2.679656918793015</v>
+        <v>2.795605515865976</v>
       </c>
       <c r="U79">
         <v>0.09</v>
@@ -7791,7 +7791,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>1.576455893304175</v>
+        <v>1.556244920313095</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7799,22 +7799,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.1041157302294346</v>
+        <v>0.1043193501521743</v>
       </c>
       <c r="C80">
-        <v>-0.8292281646296615</v>
+        <v>-1.699878353280496</v>
       </c>
       <c r="D80">
-        <v>44.50317183537034</v>
+        <v>44.3483216467195</v>
       </c>
       <c r="E80">
-        <v>54.7524</v>
+        <v>55.4682</v>
       </c>
       <c r="F80">
-        <v>55.8324</v>
+        <v>56.5482</v>
       </c>
       <c r="G80">
         <v>10.5</v>
@@ -7835,28 +7835,28 @@
         <v>7.819999999999999</v>
       </c>
       <c r="M80">
-        <v>5.024916</v>
+        <v>5.089338</v>
       </c>
       <c r="N80">
-        <v>2.795083999999999</v>
+        <v>2.730662</v>
       </c>
       <c r="O80">
-        <v>0.5031151199999998</v>
+        <v>0.49151916</v>
       </c>
       <c r="P80">
-        <v>2.291968879999999</v>
+        <v>2.23914284</v>
       </c>
       <c r="Q80">
-        <v>9.07196888</v>
+        <v>9.019142840000001</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.2115987737701573</v>
+        <v>0.2191302388198774</v>
       </c>
       <c r="T80">
-        <v>2.795605515865976</v>
+        <v>2.922596836469696</v>
       </c>
       <c r="U80">
         <v>0.09</v>
@@ -7873,7 +7873,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>1.556244920313095</v>
+        <v>1.536545617524322</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7881,22 +7881,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.1043193501521743</v>
+        <v>0.1045229700749139</v>
       </c>
       <c r="C81">
-        <v>-1.699878353280496</v>
+        <v>-2.56945466629427</v>
       </c>
       <c r="D81">
-        <v>44.3483216467195</v>
+        <v>44.19454533370573</v>
       </c>
       <c r="E81">
-        <v>55.4682</v>
+        <v>56.184</v>
       </c>
       <c r="F81">
-        <v>56.5482</v>
+        <v>57.264</v>
       </c>
       <c r="G81">
         <v>10.5</v>
@@ -7917,28 +7917,28 @@
         <v>7.819999999999999</v>
       </c>
       <c r="M81">
-        <v>5.089338</v>
+        <v>5.15376</v>
       </c>
       <c r="N81">
-        <v>2.730662</v>
+        <v>2.666239999999999</v>
       </c>
       <c r="O81">
-        <v>0.49151916</v>
+        <v>0.4799231999999998</v>
       </c>
       <c r="P81">
-        <v>2.23914284</v>
+        <v>2.186316799999999</v>
       </c>
       <c r="Q81">
-        <v>9.019142840000001</v>
+        <v>8.9663168</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.2191302388198774</v>
+        <v>0.2274148503745697</v>
       </c>
       <c r="T81">
-        <v>2.922596836469696</v>
+        <v>3.062287289133787</v>
       </c>
       <c r="U81">
         <v>0.09</v>
@@ -7955,7 +7955,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>1.536545617524322</v>
+        <v>1.517338797305268</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7963,22 +7963,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.1045229700749139</v>
+        <v>0.1446944687608415</v>
       </c>
       <c r="C82">
-        <v>-2.56945466629427</v>
+        <v>-21.23733168378165</v>
       </c>
       <c r="D82">
-        <v>44.19454533370573</v>
+        <v>26.24246831621836</v>
       </c>
       <c r="E82">
-        <v>56.184</v>
+        <v>56.89980000000001</v>
       </c>
       <c r="F82">
-        <v>57.264</v>
+        <v>57.9798</v>
       </c>
       <c r="G82">
         <v>10.5</v>
@@ -7999,45 +7999,45 @@
         <v>7.819999999999999</v>
       </c>
       <c r="M82">
-        <v>5.15376</v>
+        <v>8.511434640000001</v>
       </c>
       <c r="N82">
-        <v>2.666239999999999</v>
+        <v>-0.6914346400000015</v>
       </c>
       <c r="O82">
-        <v>0.4799231999999998</v>
+        <v>-0.1244582352000003</v>
       </c>
       <c r="P82">
-        <v>2.186316799999999</v>
+        <v>-0.5669764048000012</v>
       </c>
       <c r="Q82">
-        <v>8.9663168</v>
+        <v>6.213023595199999</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.2274148503745697</v>
+        <v>0.239216734599567</v>
       </c>
       <c r="T82">
-        <v>3.062287289133787</v>
+        <v>3.261284012009145</v>
       </c>
       <c r="U82">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V82">
-        <v>0.18</v>
+        <v>0.1653775255918548</v>
       </c>
       <c r="W82">
-        <v>0.0738</v>
+        <v>0.1225225792431157</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y82">
-        <v>1.517338797305268</v>
+        <v>0.9187640310658602</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8045,22 +8045,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.1446944687608415</v>
+        <v>0.1457044687608414</v>
       </c>
       <c r="C83">
-        <v>-21.23733168378165</v>
+        <v>-22.21843406042338</v>
       </c>
       <c r="D83">
-        <v>26.24246831621836</v>
+        <v>25.97716593957663</v>
       </c>
       <c r="E83">
-        <v>56.89980000000001</v>
+        <v>57.61560000000001</v>
       </c>
       <c r="F83">
-        <v>57.9798</v>
+        <v>58.69560000000001</v>
       </c>
       <c r="G83">
         <v>10.5</v>
@@ -8081,37 +8081,37 @@
         <v>7.819999999999999</v>
       </c>
       <c r="M83">
-        <v>8.511434640000001</v>
+        <v>8.616514080000002</v>
       </c>
       <c r="N83">
-        <v>-0.6914346400000015</v>
+        <v>-0.7965140800000023</v>
       </c>
       <c r="O83">
-        <v>-0.1244582352000003</v>
+        <v>-0.1433725344000004</v>
       </c>
       <c r="P83">
-        <v>-0.5669764048000012</v>
+        <v>-0.6531415456000019</v>
       </c>
       <c r="Q83">
-        <v>6.213023595199999</v>
+        <v>6.126858454399998</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.239216734599567</v>
+        <v>0.2499621087439873</v>
       </c>
       <c r="T83">
-        <v>3.261284012009145</v>
+        <v>3.442466457120763</v>
       </c>
       <c r="U83">
         <v>0.1468</v>
       </c>
       <c r="V83">
-        <v>0.1653775255918548</v>
+        <v>0.1633607264992712</v>
       </c>
       <c r="W83">
-        <v>0.1225225792431157</v>
+        <v>0.122818645349907</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8119,7 +8119,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.9187640310658602</v>
+        <v>0.9075595916626179</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8127,22 +8127,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.1457044687608414</v>
+        <v>0.1467144687608415</v>
       </c>
       <c r="C84">
-        <v>-22.21843406042338</v>
+        <v>-23.19422589232958</v>
       </c>
       <c r="D84">
-        <v>25.97716593957663</v>
+        <v>25.71717410767042</v>
       </c>
       <c r="E84">
-        <v>57.61560000000001</v>
+        <v>58.3314</v>
       </c>
       <c r="F84">
-        <v>58.69560000000001</v>
+        <v>59.4114</v>
       </c>
       <c r="G84">
         <v>10.5</v>
@@ -8163,37 +8163,37 @@
         <v>7.819999999999999</v>
       </c>
       <c r="M84">
-        <v>8.616514080000002</v>
+        <v>8.721593520000001</v>
       </c>
       <c r="N84">
-        <v>-0.7965140800000023</v>
+        <v>-0.9015935200000014</v>
       </c>
       <c r="O84">
-        <v>-0.1433725344000004</v>
+        <v>-0.1622868336000002</v>
       </c>
       <c r="P84">
-        <v>-0.6531415456000019</v>
+        <v>-0.7393066864000011</v>
       </c>
       <c r="Q84">
-        <v>6.126858454399998</v>
+        <v>6.040693313599999</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.2499621087439873</v>
+        <v>0.2619716445524572</v>
       </c>
       <c r="T84">
-        <v>3.442466457120763</v>
+        <v>3.644964484010221</v>
       </c>
       <c r="U84">
         <v>0.1468</v>
       </c>
       <c r="V84">
-        <v>0.1633607264992712</v>
+        <v>0.1613925249751836</v>
       </c>
       <c r="W84">
-        <v>0.122818645349907</v>
+        <v>0.1231075773336431</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8201,7 +8201,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.9075595916626179</v>
+        <v>0.8966251387510202</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8209,22 +8209,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.1467144687608415</v>
+        <v>0.1477244687608414</v>
       </c>
       <c r="C85">
-        <v>-23.19422589232958</v>
+        <v>-24.16486505082148</v>
       </c>
       <c r="D85">
-        <v>25.71717410767042</v>
+        <v>25.46233494917853</v>
       </c>
       <c r="E85">
-        <v>58.3314</v>
+        <v>59.0472</v>
       </c>
       <c r="F85">
-        <v>59.4114</v>
+        <v>60.1272</v>
       </c>
       <c r="G85">
         <v>10.5</v>
@@ -8245,37 +8245,37 @@
         <v>7.819999999999999</v>
       </c>
       <c r="M85">
-        <v>8.721593520000001</v>
+        <v>8.826672960000002</v>
       </c>
       <c r="N85">
-        <v>-0.9015935200000014</v>
+        <v>-1.006672960000002</v>
       </c>
       <c r="O85">
-        <v>-0.1622868336000002</v>
+        <v>-0.1812011328000004</v>
       </c>
       <c r="P85">
-        <v>-0.7393066864000011</v>
+        <v>-0.8254718272000018</v>
       </c>
       <c r="Q85">
-        <v>6.040693313599999</v>
+        <v>5.954528172799998</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.2619716445524572</v>
+        <v>0.2754823723369858</v>
       </c>
       <c r="T85">
-        <v>3.644964484010221</v>
+        <v>3.87277476426086</v>
       </c>
       <c r="U85">
         <v>0.1468</v>
       </c>
       <c r="V85">
-        <v>0.1613925249751836</v>
+        <v>0.1594711853921457</v>
       </c>
       <c r="W85">
-        <v>0.1231075773336431</v>
+        <v>0.123389629984433</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8283,7 +8283,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.8966251387510202</v>
+        <v>0.8859510299563651</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8291,22 +8291,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.1477244687608414</v>
+        <v>0.1487344687608415</v>
       </c>
       <c r="C86">
-        <v>-24.16486505082145</v>
+        <v>-25.13050321104379</v>
       </c>
       <c r="D86">
-        <v>25.46233494917854</v>
+        <v>25.21249678895621</v>
       </c>
       <c r="E86">
-        <v>59.0472</v>
+        <v>59.763</v>
       </c>
       <c r="F86">
-        <v>60.12719999999999</v>
+        <v>60.843</v>
       </c>
       <c r="G86">
         <v>10.5</v>
@@ -8327,37 +8327,37 @@
         <v>7.819999999999999</v>
       </c>
       <c r="M86">
-        <v>8.82667296</v>
+        <v>8.931752400000001</v>
       </c>
       <c r="N86">
-        <v>-1.00667296</v>
+        <v>-1.111752400000001</v>
       </c>
       <c r="O86">
-        <v>-0.1812011328000001</v>
+        <v>-0.2001154320000002</v>
       </c>
       <c r="P86">
-        <v>-0.8254718272000003</v>
+        <v>-0.9116369680000009</v>
       </c>
       <c r="Q86">
-        <v>5.9545281728</v>
+        <v>5.868363032</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.2754823723369856</v>
+        <v>0.2907945304927847</v>
       </c>
       <c r="T86">
-        <v>3.872774764260857</v>
+        <v>4.130959748544915</v>
       </c>
       <c r="U86">
         <v>0.1468</v>
       </c>
       <c r="V86">
-        <v>0.1594711853921457</v>
+        <v>0.1575950537992969</v>
       </c>
       <c r="W86">
-        <v>0.123389629984433</v>
+        <v>0.1236650461022632</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8365,7 +8365,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.8859510299563653</v>
+        <v>0.8755280766627609</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8373,22 +8373,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.1487344687608415</v>
+        <v>0.1497444687608414</v>
       </c>
       <c r="C87">
-        <v>-25.13050321104379</v>
+        <v>-26.09128615299749</v>
       </c>
       <c r="D87">
-        <v>25.21249678895621</v>
+        <v>24.96751384700251</v>
       </c>
       <c r="E87">
-        <v>59.763</v>
+        <v>60.4788</v>
       </c>
       <c r="F87">
-        <v>60.843</v>
+        <v>61.5588</v>
       </c>
       <c r="G87">
         <v>10.5</v>
@@ -8409,37 +8409,37 @@
         <v>7.819999999999999</v>
       </c>
       <c r="M87">
-        <v>8.931752400000001</v>
+        <v>9.036831840000001</v>
       </c>
       <c r="N87">
-        <v>-1.111752400000001</v>
+        <v>-1.216831840000002</v>
       </c>
       <c r="O87">
-        <v>-0.2001154320000002</v>
+        <v>-0.2190297312000004</v>
       </c>
       <c r="P87">
-        <v>-0.9116369680000009</v>
+        <v>-0.9978021088000016</v>
       </c>
       <c r="Q87">
-        <v>5.868363032</v>
+        <v>5.782197891199998</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.2907945304927847</v>
+        <v>0.3082941398136979</v>
       </c>
       <c r="T87">
-        <v>4.130959748544915</v>
+        <v>4.426028302012408</v>
       </c>
       <c r="U87">
         <v>0.1468</v>
       </c>
       <c r="V87">
-        <v>0.1575950537992969</v>
+        <v>0.1557625531737237</v>
       </c>
       <c r="W87">
-        <v>0.1236650461022632</v>
+        <v>0.1239340571940974</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8447,7 +8447,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.8755280766627609</v>
+        <v>0.8653475176317985</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8455,22 +8455,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.1497444687608414</v>
+        <v>0.1507544687608414</v>
       </c>
       <c r="C88">
-        <v>-26.09128615299749</v>
+        <v>-27.04735404519115</v>
       </c>
       <c r="D88">
-        <v>24.96751384700251</v>
+        <v>24.72724595480885</v>
       </c>
       <c r="E88">
-        <v>60.4788</v>
+        <v>61.1946</v>
       </c>
       <c r="F88">
-        <v>61.5588</v>
+        <v>62.2746</v>
       </c>
       <c r="G88">
         <v>10.5</v>
@@ -8491,37 +8491,37 @@
         <v>7.819999999999999</v>
       </c>
       <c r="M88">
-        <v>9.036831840000001</v>
+        <v>9.14191128</v>
       </c>
       <c r="N88">
-        <v>-1.216831840000002</v>
+        <v>-1.321911280000001</v>
       </c>
       <c r="O88">
-        <v>-0.2190297312000004</v>
+        <v>-0.2379440304000002</v>
       </c>
       <c r="P88">
-        <v>-0.9978021088000016</v>
+        <v>-1.083967249600001</v>
       </c>
       <c r="Q88">
-        <v>5.782197891199998</v>
+        <v>5.6960327504</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.3082941398136979</v>
+        <v>0.3284859967224439</v>
       </c>
       <c r="T88">
-        <v>4.426028302012408</v>
+        <v>4.766492017551824</v>
       </c>
       <c r="U88">
         <v>0.1468</v>
       </c>
       <c r="V88">
-        <v>0.1557625531737237</v>
+        <v>0.1539721789993131</v>
       </c>
       <c r="W88">
-        <v>0.1239340571940974</v>
+        <v>0.1241968841229008</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8529,7 +8529,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.8653475176317985</v>
+        <v>0.8554009944406284</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8537,22 +8537,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.1507544687608414</v>
+        <v>0.1517644687608414</v>
       </c>
       <c r="C89">
-        <v>-27.04735404519115</v>
+        <v>-27.99884171207054</v>
       </c>
       <c r="D89">
-        <v>24.72724595480885</v>
+        <v>24.49155828792946</v>
       </c>
       <c r="E89">
-        <v>61.1946</v>
+        <v>61.9104</v>
       </c>
       <c r="F89">
-        <v>62.2746</v>
+        <v>62.9904</v>
       </c>
       <c r="G89">
         <v>10.5</v>
@@ -8573,37 +8573,37 @@
         <v>7.819999999999999</v>
       </c>
       <c r="M89">
-        <v>9.14191128</v>
+        <v>9.246990720000001</v>
       </c>
       <c r="N89">
-        <v>-1.321911280000001</v>
+        <v>-1.426990720000002</v>
       </c>
       <c r="O89">
-        <v>-0.2379440304000002</v>
+        <v>-0.2568583296000003</v>
       </c>
       <c r="P89">
-        <v>-1.083967249600001</v>
+        <v>-1.170132390400001</v>
       </c>
       <c r="Q89">
-        <v>5.6960327504</v>
+        <v>5.609867609599998</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.3284859967224439</v>
+        <v>0.3520431631159809</v>
       </c>
       <c r="T89">
-        <v>4.766492017551824</v>
+        <v>5.163699685681144</v>
       </c>
       <c r="U89">
         <v>0.1468</v>
       </c>
       <c r="V89">
-        <v>0.1539721789993131</v>
+        <v>0.1522224951470482</v>
       </c>
       <c r="W89">
-        <v>0.1241968841229008</v>
+        <v>0.1244537377124133</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8611,7 +8611,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.8554009944406284</v>
+        <v>0.8456805285947122</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8619,22 +8619,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.1517644687608414</v>
+        <v>0.1527744687608414</v>
       </c>
       <c r="C90">
-        <v>-27.99884171207054</v>
+        <v>-28.94587888629864</v>
       </c>
       <c r="D90">
-        <v>24.49155828792946</v>
+        <v>24.26032111370136</v>
       </c>
       <c r="E90">
-        <v>61.9104</v>
+        <v>62.6262</v>
       </c>
       <c r="F90">
-        <v>62.9904</v>
+        <v>63.7062</v>
       </c>
       <c r="G90">
         <v>10.5</v>
@@ -8655,37 +8655,37 @@
         <v>7.819999999999999</v>
       </c>
       <c r="M90">
-        <v>9.246990720000001</v>
+        <v>9.352070160000002</v>
       </c>
       <c r="N90">
-        <v>-1.426990720000002</v>
+        <v>-1.532070160000003</v>
       </c>
       <c r="O90">
-        <v>-0.2568583296000003</v>
+        <v>-0.2757726288000005</v>
       </c>
       <c r="P90">
-        <v>-1.170132390400001</v>
+        <v>-1.256297531200002</v>
       </c>
       <c r="Q90">
-        <v>5.609867609599998</v>
+        <v>5.523702468799998</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.3520431631159809</v>
+        <v>0.3798834506719792</v>
       </c>
       <c r="T90">
-        <v>5.163699685681144</v>
+        <v>5.633126929833976</v>
       </c>
       <c r="U90">
         <v>0.1468</v>
       </c>
       <c r="V90">
-        <v>0.1522224951470482</v>
+        <v>0.1505121300330364</v>
       </c>
       <c r="W90">
-        <v>0.1244537377124133</v>
+        <v>0.1247048193111503</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8693,7 +8693,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.8456805285947122</v>
+        <v>0.8361785001835356</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8701,22 +8701,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.1527744687608414</v>
+        <v>0.1537844687608415</v>
       </c>
       <c r="C91">
-        <v>-28.94587888629864</v>
+        <v>-29.88859044687784</v>
       </c>
       <c r="D91">
-        <v>24.26032111370136</v>
+        <v>24.03340955312215</v>
       </c>
       <c r="E91">
-        <v>62.6262</v>
+        <v>63.342</v>
       </c>
       <c r="F91">
-        <v>63.7062</v>
+        <v>64.422</v>
       </c>
       <c r="G91">
         <v>10.5</v>
@@ -8737,37 +8737,37 @@
         <v>7.819999999999999</v>
       </c>
       <c r="M91">
-        <v>9.352070160000002</v>
+        <v>9.457149600000001</v>
       </c>
       <c r="N91">
-        <v>-1.532070160000003</v>
+        <v>-1.637149600000002</v>
       </c>
       <c r="O91">
-        <v>-0.2757726288000005</v>
+        <v>-0.2946869280000003</v>
       </c>
       <c r="P91">
-        <v>-1.256297531200002</v>
+        <v>-1.342462672000001</v>
       </c>
       <c r="Q91">
-        <v>5.523702468799998</v>
+        <v>5.437537327999999</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.3798834506719792</v>
+        <v>0.4132917957391771</v>
       </c>
       <c r="T91">
-        <v>5.633126929833976</v>
+        <v>6.196439622817373</v>
       </c>
       <c r="U91">
         <v>0.1468</v>
       </c>
       <c r="V91">
-        <v>0.1505121300330364</v>
+        <v>0.1488397730326693</v>
       </c>
       <c r="W91">
-        <v>0.1247048193111503</v>
+        <v>0.1249503213188042</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8775,7 +8775,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.8361785001835356</v>
+        <v>0.8268876279592742</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8783,22 +8783,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.1537844687608415</v>
+        <v>0.1547944687608414</v>
       </c>
       <c r="C92">
-        <v>-29.88859044687784</v>
+        <v>-30.82709664403281</v>
       </c>
       <c r="D92">
-        <v>24.03340955312215</v>
+        <v>23.81070335596719</v>
       </c>
       <c r="E92">
-        <v>63.342</v>
+        <v>64.0578</v>
       </c>
       <c r="F92">
-        <v>64.422</v>
+        <v>65.1378</v>
       </c>
       <c r="G92">
         <v>10.5</v>
@@ -8819,37 +8819,37 @@
         <v>7.819999999999999</v>
       </c>
       <c r="M92">
-        <v>9.457149600000001</v>
+        <v>9.56222904</v>
       </c>
       <c r="N92">
-        <v>-1.637149600000002</v>
+        <v>-1.742229040000001</v>
       </c>
       <c r="O92">
-        <v>-0.2946869280000003</v>
+        <v>-0.3136012272000001</v>
       </c>
       <c r="P92">
-        <v>-1.342462672000001</v>
+        <v>-1.428627812800001</v>
       </c>
       <c r="Q92">
-        <v>5.437537327999999</v>
+        <v>5.3513721872</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.4132917957391771</v>
+        <v>0.4541242174879747</v>
       </c>
       <c r="T92">
-        <v>6.196439622817373</v>
+        <v>6.884932914241527</v>
       </c>
       <c r="U92">
         <v>0.1468</v>
       </c>
       <c r="V92">
-        <v>0.1488397730326693</v>
+        <v>0.1472041711312115</v>
       </c>
       <c r="W92">
-        <v>0.1249503213188042</v>
+        <v>0.1251904276779382</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8857,7 +8857,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.8268876279592742</v>
+        <v>0.8178009507289525</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8865,22 +8865,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.1547944687608414</v>
+        <v>0.1558044687608414</v>
       </c>
       <c r="C93">
-        <v>-30.82709664403281</v>
+        <v>-31.76151331170485</v>
       </c>
       <c r="D93">
-        <v>23.81070335596719</v>
+        <v>23.59208668829516</v>
       </c>
       <c r="E93">
-        <v>64.0578</v>
+        <v>64.7736</v>
       </c>
       <c r="F93">
-        <v>65.1378</v>
+        <v>65.8536</v>
       </c>
       <c r="G93">
         <v>10.5</v>
@@ -8901,37 +8901,37 @@
         <v>7.819999999999999</v>
       </c>
       <c r="M93">
-        <v>9.56222904</v>
+        <v>9.667308480000001</v>
       </c>
       <c r="N93">
-        <v>-1.742229040000001</v>
+        <v>-1.847308480000001</v>
       </c>
       <c r="O93">
-        <v>-0.3136012272000001</v>
+        <v>-0.3325155264000003</v>
       </c>
       <c r="P93">
-        <v>-1.428627812800001</v>
+        <v>-1.514792953600001</v>
       </c>
       <c r="Q93">
-        <v>5.3513721872</v>
+        <v>5.265207046399999</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.4541242174879747</v>
+        <v>0.5051647446739715</v>
       </c>
       <c r="T93">
-        <v>6.884932914241527</v>
+        <v>7.74554952852172</v>
       </c>
       <c r="U93">
         <v>0.1468</v>
       </c>
       <c r="V93">
-        <v>0.1472041711312115</v>
+        <v>0.1456041257928287</v>
       </c>
       <c r="W93">
-        <v>0.1251904276779382</v>
+        <v>0.1254253143336128</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8939,7 +8939,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.8178009507289525</v>
+        <v>0.8089118099601595</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8947,22 +8947,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.1558044687608414</v>
+        <v>0.1568144687608414</v>
       </c>
       <c r="C94">
-        <v>-31.76151331170485</v>
+        <v>-32.69195206844664</v>
       </c>
       <c r="D94">
-        <v>23.59208668829516</v>
+        <v>23.37744793155336</v>
       </c>
       <c r="E94">
-        <v>64.7736</v>
+        <v>65.4894</v>
       </c>
       <c r="F94">
-        <v>65.8536</v>
+        <v>66.5694</v>
       </c>
       <c r="G94">
         <v>10.5</v>
@@ -8983,37 +8983,37 @@
         <v>7.819999999999999</v>
       </c>
       <c r="M94">
-        <v>9.667308480000001</v>
+        <v>9.772387920000002</v>
       </c>
       <c r="N94">
-        <v>-1.847308480000001</v>
+        <v>-1.952387920000002</v>
       </c>
       <c r="O94">
-        <v>-0.3325155264000003</v>
+        <v>-0.3514298256000004</v>
       </c>
       <c r="P94">
-        <v>-1.514792953600001</v>
+        <v>-1.600958094400002</v>
       </c>
       <c r="Q94">
-        <v>5.265207046399999</v>
+        <v>5.179041905599998</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.5051647446739715</v>
+        <v>0.5707882796273961</v>
       </c>
       <c r="T94">
-        <v>7.74554952852172</v>
+        <v>8.852056604024824</v>
       </c>
       <c r="U94">
         <v>0.1468</v>
       </c>
       <c r="V94">
-        <v>0.1456041257928287</v>
+        <v>0.1440384900316155</v>
       </c>
       <c r="W94">
-        <v>0.1254253143336128</v>
+        <v>0.1256551496633589</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9021,7 +9021,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.8089118099601595</v>
+        <v>0.800213833508975</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9029,22 +9029,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.1568144687608414</v>
+        <v>0.2101130873904153</v>
       </c>
       <c r="C95">
-        <v>-32.69195206844664</v>
+        <v>-40.99074926985681</v>
       </c>
       <c r="D95">
-        <v>23.37744793155336</v>
+        <v>15.79445073014319</v>
       </c>
       <c r="E95">
-        <v>65.4894</v>
+        <v>66.2052</v>
       </c>
       <c r="F95">
-        <v>66.5694</v>
+        <v>67.2852</v>
       </c>
       <c r="G95">
         <v>10.5</v>
@@ -9065,45 +9065,45 @@
         <v>7.819999999999999</v>
       </c>
       <c r="M95">
-        <v>9.772387920000002</v>
+        <v>13.51086816</v>
       </c>
       <c r="N95">
-        <v>-1.952387920000002</v>
+        <v>-5.690868160000002</v>
       </c>
       <c r="O95">
-        <v>-0.3514298256000004</v>
+        <v>-1.0243562688</v>
       </c>
       <c r="P95">
-        <v>-1.600958094400002</v>
+        <v>-4.666511891200002</v>
       </c>
       <c r="Q95">
-        <v>5.179041905599998</v>
+        <v>2.113488108799999</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.5707882796273961</v>
+        <v>0.6837633033915269</v>
       </c>
       <c r="T95">
-        <v>8.852056604024824</v>
+        <v>10.75697780704847</v>
       </c>
       <c r="U95">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V95">
-        <v>0.1440384900316155</v>
+        <v>0.1041827944237744</v>
       </c>
       <c r="W95">
-        <v>0.1256551496633589</v>
+        <v>0.1798800948797061</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y95">
-        <v>0.800213833508975</v>
+        <v>0.5787933023543025</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9111,22 +9111,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2101130873904153</v>
+        <v>0.2116630873904153</v>
       </c>
       <c r="C96">
-        <v>-40.99074926985681</v>
+        <v>-41.85414931165572</v>
       </c>
       <c r="D96">
-        <v>15.79445073014319</v>
+        <v>15.64685068834429</v>
       </c>
       <c r="E96">
-        <v>66.2052</v>
+        <v>66.92100000000001</v>
       </c>
       <c r="F96">
-        <v>67.2852</v>
+        <v>68.001</v>
       </c>
       <c r="G96">
         <v>10.5</v>
@@ -9147,37 +9147,37 @@
         <v>7.819999999999999</v>
       </c>
       <c r="M96">
-        <v>13.51086816</v>
+        <v>13.6546008</v>
       </c>
       <c r="N96">
-        <v>-5.690868160000002</v>
+        <v>-5.834600800000001</v>
       </c>
       <c r="O96">
-        <v>-1.0243562688</v>
+        <v>-1.050228144</v>
       </c>
       <c r="P96">
-        <v>-4.666511891200002</v>
+        <v>-4.784372656000001</v>
       </c>
       <c r="Q96">
-        <v>2.113488108799999</v>
+        <v>1.995627343999999</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.6837633033915269</v>
+        <v>0.8113559640698327</v>
       </c>
       <c r="T96">
-        <v>10.75697780704847</v>
+        <v>12.90837336845817</v>
       </c>
       <c r="U96">
         <v>0.2008</v>
       </c>
       <c r="V96">
-        <v>0.1041827944237744</v>
+        <v>0.10308613342984</v>
       </c>
       <c r="W96">
-        <v>0.1798800948797061</v>
+        <v>0.1801003044072881</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9185,7 +9185,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.5787933023543025</v>
+        <v>0.5727007412768887</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9193,22 +9193,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2116630873904153</v>
+        <v>0.2132130873904153</v>
       </c>
       <c r="C97">
-        <v>-41.85414931165572</v>
+        <v>-42.71481623302356</v>
       </c>
       <c r="D97">
-        <v>15.64685068834429</v>
+        <v>15.50198376697645</v>
       </c>
       <c r="E97">
-        <v>66.92100000000001</v>
+        <v>67.63680000000001</v>
       </c>
       <c r="F97">
-        <v>68.001</v>
+        <v>68.71680000000001</v>
       </c>
       <c r="G97">
         <v>10.5</v>
@@ -9229,37 +9229,37 @@
         <v>7.819999999999999</v>
       </c>
       <c r="M97">
-        <v>13.6546008</v>
+        <v>13.79833344</v>
       </c>
       <c r="N97">
-        <v>-5.834600800000001</v>
+        <v>-5.978333440000003</v>
       </c>
       <c r="O97">
-        <v>-1.050228144</v>
+        <v>-1.076100019200001</v>
       </c>
       <c r="P97">
-        <v>-4.784372656000001</v>
+        <v>-4.902233420800002</v>
       </c>
       <c r="Q97">
-        <v>1.995627343999999</v>
+        <v>1.877766579199998</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.8113559640698327</v>
+        <v>1.002744955087291</v>
       </c>
       <c r="T97">
-        <v>12.90837336845817</v>
+        <v>16.13546671057273</v>
       </c>
       <c r="U97">
         <v>0.2008</v>
       </c>
       <c r="V97">
-        <v>0.10308613342984</v>
+        <v>0.1020123195399458</v>
       </c>
       <c r="W97">
-        <v>0.1801003044072881</v>
+        <v>0.1803159262363789</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9267,7 +9267,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.5727007412768887</v>
+        <v>0.5667351085552546</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9275,22 +9275,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2132130873904153</v>
+        <v>0.2147630873904153</v>
       </c>
       <c r="C98">
-        <v>-42.71481623302354</v>
+        <v>-43.57282525163181</v>
       </c>
       <c r="D98">
-        <v>15.50198376697645</v>
+        <v>15.35977474836818</v>
       </c>
       <c r="E98">
-        <v>67.63679999999999</v>
+        <v>68.3526</v>
       </c>
       <c r="F98">
-        <v>68.71679999999999</v>
+        <v>69.43259999999999</v>
       </c>
       <c r="G98">
         <v>10.5</v>
@@ -9311,37 +9311,37 @@
         <v>7.819999999999999</v>
       </c>
       <c r="M98">
-        <v>13.79833344</v>
+        <v>13.94206608</v>
       </c>
       <c r="N98">
-        <v>-5.978333439999999</v>
+        <v>-6.122066080000001</v>
       </c>
       <c r="O98">
-        <v>-1.0761000192</v>
+        <v>-1.1019718944</v>
       </c>
       <c r="P98">
-        <v>-4.902233420799999</v>
+        <v>-5.020094185600001</v>
       </c>
       <c r="Q98">
-        <v>1.877766579200001</v>
+        <v>1.7599058144</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.002744955087289</v>
+        <v>1.321726606783052</v>
       </c>
       <c r="T98">
-        <v>16.13546671057268</v>
+        <v>21.51395561409691</v>
       </c>
       <c r="U98">
         <v>0.2008</v>
       </c>
       <c r="V98">
-        <v>0.1020123195399458</v>
+        <v>0.1009606461426268</v>
       </c>
       <c r="W98">
-        <v>0.1803159262363789</v>
+        <v>0.1805271022545605</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9349,7 +9349,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.5667351085552547</v>
+        <v>0.5608924785701488</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9357,22 +9357,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2147630873904153</v>
+        <v>0.2163130873904153</v>
       </c>
       <c r="C99">
-        <v>-43.57282525163181</v>
+        <v>-44.4282488501739</v>
       </c>
       <c r="D99">
-        <v>15.35977474836818</v>
+        <v>15.22015114982609</v>
       </c>
       <c r="E99">
-        <v>68.3526</v>
+        <v>69.0684</v>
       </c>
       <c r="F99">
-        <v>69.43259999999999</v>
+        <v>70.1484</v>
       </c>
       <c r="G99">
         <v>10.5</v>
@@ -9393,37 +9393,37 @@
         <v>7.819999999999999</v>
       </c>
       <c r="M99">
-        <v>13.94206608</v>
+        <v>14.08579872</v>
       </c>
       <c r="N99">
-        <v>-6.122066080000001</v>
+        <v>-6.26579872</v>
       </c>
       <c r="O99">
-        <v>-1.1019718944</v>
+        <v>-1.1278437696</v>
       </c>
       <c r="P99">
-        <v>-5.020094185600001</v>
+        <v>-5.1379549504</v>
       </c>
       <c r="Q99">
-        <v>1.7599058144</v>
+        <v>1.6420450496</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.321726606783052</v>
+        <v>1.959689910174577</v>
       </c>
       <c r="T99">
-        <v>21.51395561409691</v>
+        <v>32.27093342114536</v>
       </c>
       <c r="U99">
         <v>0.2008</v>
       </c>
       <c r="V99">
-        <v>0.1009606461426268</v>
+        <v>0.09993043546770204</v>
       </c>
       <c r="W99">
-        <v>0.1805271022545605</v>
+        <v>0.1807339685580854</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9431,7 +9431,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.5608924785701488</v>
+        <v>0.555169085931678</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9439,22 +9439,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2163130873904153</v>
+        <v>0.2178630873904153</v>
       </c>
       <c r="C100">
-        <v>-44.4282488501739</v>
+        <v>-45.2811568995529</v>
       </c>
       <c r="D100">
-        <v>15.22015114982609</v>
+        <v>15.0830431004471</v>
       </c>
       <c r="E100">
-        <v>69.0684</v>
+        <v>69.7842</v>
       </c>
       <c r="F100">
-        <v>70.1484</v>
+        <v>70.8642</v>
       </c>
       <c r="G100">
         <v>10.5</v>
@@ -9475,37 +9475,37 @@
         <v>7.819999999999999</v>
       </c>
       <c r="M100">
-        <v>14.08579872</v>
+        <v>14.22953136</v>
       </c>
       <c r="N100">
-        <v>-6.26579872</v>
+        <v>-6.40953136</v>
       </c>
       <c r="O100">
-        <v>-1.1278437696</v>
+        <v>-1.1537156448</v>
       </c>
       <c r="P100">
-        <v>-5.1379549504</v>
+        <v>-5.2558157152</v>
       </c>
       <c r="Q100">
-        <v>1.6420450496</v>
+        <v>1.5241842848</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>1.959689910174577</v>
+        <v>3.873579820349154</v>
       </c>
       <c r="T100">
-        <v>32.27093342114536</v>
+        <v>64.54186684229072</v>
       </c>
       <c r="U100">
         <v>0.2008</v>
       </c>
       <c r="V100">
-        <v>0.09993043546770204</v>
+        <v>0.09892103712964445</v>
       </c>
       <c r="W100">
-        <v>0.1807339685580854</v>
+        <v>0.1809366557443674</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9513,91 +9513,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.555169085931678</v>
+        <v>0.5495613173869136</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2178630873904153</v>
-      </c>
-      <c r="C101">
-        <v>-45.2811568995529</v>
-      </c>
-      <c r="D101">
-        <v>15.0830431004471</v>
-      </c>
-      <c r="E101">
-        <v>69.7842</v>
-      </c>
-      <c r="F101">
-        <v>70.8642</v>
-      </c>
-      <c r="G101">
-        <v>10.5</v>
-      </c>
-      <c r="H101">
-        <v>70.5</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>14.6</v>
-      </c>
-      <c r="K101">
-        <v>6.78</v>
-      </c>
-      <c r="L101">
-        <v>7.819999999999999</v>
-      </c>
-      <c r="M101">
-        <v>14.22953136</v>
-      </c>
-      <c r="N101">
-        <v>-6.40953136</v>
-      </c>
-      <c r="O101">
-        <v>-1.1537156448</v>
-      </c>
-      <c r="P101">
-        <v>-5.2558157152</v>
-      </c>
-      <c r="Q101">
-        <v>1.5241842848</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>3.873579820349154</v>
-      </c>
-      <c r="T101">
-        <v>64.54186684229072</v>
-      </c>
-      <c r="U101">
-        <v>0.2008</v>
-      </c>
-      <c r="V101">
-        <v>0.09892103712964445</v>
-      </c>
-      <c r="W101">
-        <v>0.1809366557443674</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>C2/C</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.5495613173869136</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
